--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="259">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,12 @@
     <t>['23', '83']</t>
   </si>
   <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['27', '30', '81']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -782,6 +788,9 @@
   </si>
   <si>
     <t>['3', '10', '22']</t>
+  </si>
+  <si>
+    <t>['40', '81', '90+6', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1811,7 +1820,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2095,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ5">
         <v>1.09</v>
@@ -2429,7 +2438,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2716,7 +2725,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ8">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2841,7 +2850,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -2919,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3253,7 +3262,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3331,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3459,7 +3468,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3665,7 +3674,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4077,7 +4086,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4155,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15">
         <v>1.09</v>
@@ -4489,7 +4498,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4567,10 +4576,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR17">
         <v>1.07</v>
@@ -5107,7 +5116,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5313,7 +5322,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5394,7 +5403,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ21">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR21">
         <v>1.39</v>
@@ -5519,7 +5528,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5597,7 +5606,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22">
         <v>1.2</v>
@@ -5931,7 +5940,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6012,7 +6021,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ24">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
         <v>1.14</v>
@@ -6137,7 +6146,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6424,7 +6433,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR26">
         <v>1.12</v>
@@ -6833,7 +6842,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ28">
         <v>0.73</v>
@@ -7039,7 +7048,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ29">
         <v>1.09</v>
@@ -7167,7 +7176,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7245,7 +7254,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ30">
         <v>0.75</v>
@@ -7579,7 +7588,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7657,7 +7666,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32">
         <v>0.73</v>
@@ -7863,7 +7872,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
         <v>0.73</v>
@@ -7991,7 +8000,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8197,7 +8206,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8278,7 +8287,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ35">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR35">
         <v>1.32</v>
@@ -8403,7 +8412,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8609,7 +8618,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8815,7 +8824,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -8896,7 +8905,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ38">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR38">
         <v>1.42</v>
@@ -9227,7 +9236,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9305,10 +9314,10 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ40">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
         <v>0.9399999999999999</v>
@@ -9433,7 +9442,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9511,10 +9520,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ41">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR41">
         <v>1.12</v>
@@ -9639,7 +9648,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9845,7 +9854,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -9923,10 +9932,10 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ43">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR43">
         <v>1.4</v>
@@ -10051,7 +10060,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10463,7 +10472,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10669,7 +10678,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11081,7 +11090,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11699,7 +11708,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11905,7 +11914,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -11983,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ53">
         <v>0.75</v>
@@ -12192,7 +12201,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR54">
         <v>1.17</v>
@@ -12395,7 +12404,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ55">
         <v>0.73</v>
@@ -12523,7 +12532,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12604,7 +12613,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ56">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12729,7 +12738,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12935,7 +12944,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13219,7 +13228,7 @@
         <v>0.25</v>
       </c>
       <c r="AP59">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
         <v>1.09</v>
@@ -13347,7 +13356,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13425,7 +13434,7 @@
         <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ60">
         <v>0.73</v>
@@ -13553,7 +13562,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13634,7 +13643,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
         <v>1.15</v>
@@ -13965,7 +13974,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14171,7 +14180,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14455,7 +14464,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
@@ -14583,7 +14592,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14789,7 +14798,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -14867,10 +14876,10 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ67">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR67">
         <v>1.3</v>
@@ -15201,7 +15210,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15279,7 +15288,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ69">
         <v>0.91</v>
@@ -15407,7 +15416,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15613,7 +15622,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15819,7 +15828,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15900,7 +15909,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16437,7 +16446,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16515,10 +16524,10 @@
         <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ75">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16724,7 +16733,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR76">
         <v>1.75</v>
@@ -16849,7 +16858,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16927,7 +16936,7 @@
         <v>2.5</v>
       </c>
       <c r="AP77">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17055,7 +17064,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17261,7 +17270,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17342,7 +17351,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ79">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR79">
         <v>1.56</v>
@@ -17467,7 +17476,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17545,7 +17554,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ80">
         <v>1.2</v>
@@ -18085,7 +18094,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18291,7 +18300,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18497,7 +18506,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18703,7 +18712,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19115,7 +19124,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19196,7 +19205,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ88">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR88">
         <v>1.42</v>
@@ -19321,7 +19330,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19402,7 +19411,7 @@
         <v>2</v>
       </c>
       <c r="AQ89">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19605,10 +19614,10 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ90">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
@@ -20557,7 +20566,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20635,7 +20644,7 @@
         <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
         <v>1.18</v>
@@ -20763,7 +20772,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20969,7 +20978,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21047,7 +21056,7 @@
         <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ97">
         <v>1.09</v>
@@ -21175,7 +21184,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21256,7 +21265,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ98">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR98">
         <v>1.21</v>
@@ -21587,7 +21596,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21793,7 +21802,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21871,7 +21880,7 @@
         <v>0.88</v>
       </c>
       <c r="AP101">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ101">
         <v>0.91</v>
@@ -22205,7 +22214,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22492,7 +22501,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR104">
         <v>1.42</v>
@@ -22823,7 +22832,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23110,7 +23119,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ107">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR107">
         <v>2.23</v>
@@ -23235,7 +23244,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23647,7 +23656,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23728,7 +23737,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ110">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR110">
         <v>1.25</v>
@@ -23931,7 +23940,7 @@
         <v>1.43</v>
       </c>
       <c r="AP111">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ111">
         <v>1.18</v>
@@ -24059,7 +24068,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24137,7 +24146,7 @@
         <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
         <v>0.73</v>
@@ -24549,7 +24558,7 @@
         <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ114">
         <v>0.75</v>
@@ -24677,7 +24686,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24883,7 +24892,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -24961,7 +24970,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ116">
         <v>1.09</v>
@@ -25788,7 +25797,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ120">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR120">
         <v>1.65</v>
@@ -25994,7 +26003,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ121">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR121">
         <v>2.04</v>
@@ -26119,7 +26128,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26325,7 +26334,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26406,7 +26415,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ123">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR123">
         <v>1.36</v>
@@ -26531,7 +26540,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26609,7 +26618,7 @@
         <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ124">
         <v>1.18</v>
@@ -27149,7 +27158,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27355,7 +27364,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27561,7 +27570,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -27848,7 +27857,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ130">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR130">
         <v>1.4</v>
@@ -28054,7 +28063,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ131">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR131">
         <v>2.28</v>
@@ -28336,6 +28345,624 @@
       </c>
       <c r="BP132">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7480274</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45668.39583333334</v>
+      </c>
+      <c r="F133">
+        <v>23</v>
+      </c>
+      <c r="G133" t="s">
+        <v>77</v>
+      </c>
+      <c r="H133" t="s">
+        <v>74</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>4</v>
+      </c>
+      <c r="N133">
+        <v>5</v>
+      </c>
+      <c r="O133" t="s">
+        <v>185</v>
+      </c>
+      <c r="P133" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q133">
+        <v>10</v>
+      </c>
+      <c r="R133">
+        <v>2.95</v>
+      </c>
+      <c r="S133">
+        <v>1.49</v>
+      </c>
+      <c r="T133">
+        <v>1.22</v>
+      </c>
+      <c r="U133">
+        <v>3.9</v>
+      </c>
+      <c r="V133">
+        <v>1.98</v>
+      </c>
+      <c r="W133">
+        <v>1.71</v>
+      </c>
+      <c r="X133">
+        <v>4.2</v>
+      </c>
+      <c r="Y133">
+        <v>1.2</v>
+      </c>
+      <c r="Z133">
+        <v>15</v>
+      </c>
+      <c r="AA133">
+        <v>7</v>
+      </c>
+      <c r="AB133">
+        <v>1.14</v>
+      </c>
+      <c r="AC133">
+        <v>0</v>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133">
+        <v>1.12</v>
+      </c>
+      <c r="AF133">
+        <v>6</v>
+      </c>
+      <c r="AG133">
+        <v>1.35</v>
+      </c>
+      <c r="AH133">
+        <v>3.04</v>
+      </c>
+      <c r="AI133">
+        <v>2.15</v>
+      </c>
+      <c r="AJ133">
+        <v>1.61</v>
+      </c>
+      <c r="AK133">
+        <v>5.5</v>
+      </c>
+      <c r="AL133">
+        <v>1.07</v>
+      </c>
+      <c r="AM133">
+        <v>1.02</v>
+      </c>
+      <c r="AN133">
+        <v>1.18</v>
+      </c>
+      <c r="AO133">
+        <v>2.5</v>
+      </c>
+      <c r="AP133">
+        <v>1.08</v>
+      </c>
+      <c r="AQ133">
+        <v>2.55</v>
+      </c>
+      <c r="AR133">
+        <v>1.25</v>
+      </c>
+      <c r="AS133">
+        <v>1.79</v>
+      </c>
+      <c r="AT133">
+        <v>3.04</v>
+      </c>
+      <c r="AU133">
+        <v>2</v>
+      </c>
+      <c r="AV133">
+        <v>15</v>
+      </c>
+      <c r="AW133">
+        <v>5</v>
+      </c>
+      <c r="AX133">
+        <v>14</v>
+      </c>
+      <c r="AY133">
+        <v>8</v>
+      </c>
+      <c r="AZ133">
+        <v>37</v>
+      </c>
+      <c r="BA133">
+        <v>6</v>
+      </c>
+      <c r="BB133">
+        <v>7</v>
+      </c>
+      <c r="BC133">
+        <v>13</v>
+      </c>
+      <c r="BD133">
+        <v>0</v>
+      </c>
+      <c r="BE133">
+        <v>0</v>
+      </c>
+      <c r="BF133">
+        <v>0</v>
+      </c>
+      <c r="BG133">
+        <v>0</v>
+      </c>
+      <c r="BH133">
+        <v>0</v>
+      </c>
+      <c r="BI133">
+        <v>0</v>
+      </c>
+      <c r="BJ133">
+        <v>0</v>
+      </c>
+      <c r="BK133">
+        <v>0</v>
+      </c>
+      <c r="BL133">
+        <v>0</v>
+      </c>
+      <c r="BM133">
+        <v>0</v>
+      </c>
+      <c r="BN133">
+        <v>0</v>
+      </c>
+      <c r="BO133">
+        <v>0</v>
+      </c>
+      <c r="BP133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7480275</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45668.5</v>
+      </c>
+      <c r="F134">
+        <v>23</v>
+      </c>
+      <c r="G134" t="s">
+        <v>73</v>
+      </c>
+      <c r="H134" t="s">
+        <v>72</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>82</v>
+      </c>
+      <c r="P134" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q134">
+        <v>3</v>
+      </c>
+      <c r="R134">
+        <v>2.05</v>
+      </c>
+      <c r="S134">
+        <v>3.3</v>
+      </c>
+      <c r="T134">
+        <v>1.4</v>
+      </c>
+      <c r="U134">
+        <v>2.7</v>
+      </c>
+      <c r="V134">
+        <v>2.8</v>
+      </c>
+      <c r="W134">
+        <v>1.37</v>
+      </c>
+      <c r="X134">
+        <v>7.25</v>
+      </c>
+      <c r="Y134">
+        <v>1.08</v>
+      </c>
+      <c r="Z134">
+        <v>2.54</v>
+      </c>
+      <c r="AA134">
+        <v>2.97</v>
+      </c>
+      <c r="AB134">
+        <v>3.08</v>
+      </c>
+      <c r="AC134">
+        <v>1.06</v>
+      </c>
+      <c r="AD134">
+        <v>8.5</v>
+      </c>
+      <c r="AE134">
+        <v>1.3</v>
+      </c>
+      <c r="AF134">
+        <v>3.35</v>
+      </c>
+      <c r="AG134">
+        <v>1.85</v>
+      </c>
+      <c r="AH134">
+        <v>1.85</v>
+      </c>
+      <c r="AI134">
+        <v>1.73</v>
+      </c>
+      <c r="AJ134">
+        <v>1.95</v>
+      </c>
+      <c r="AK134">
+        <v>1.42</v>
+      </c>
+      <c r="AL134">
+        <v>1.31</v>
+      </c>
+      <c r="AM134">
+        <v>1.52</v>
+      </c>
+      <c r="AN134">
+        <v>1.55</v>
+      </c>
+      <c r="AO134">
+        <v>1.45</v>
+      </c>
+      <c r="AP134">
+        <v>1.42</v>
+      </c>
+      <c r="AQ134">
+        <v>1.58</v>
+      </c>
+      <c r="AR134">
+        <v>1.22</v>
+      </c>
+      <c r="AS134">
+        <v>1.21</v>
+      </c>
+      <c r="AT134">
+        <v>2.43</v>
+      </c>
+      <c r="AU134">
+        <v>4</v>
+      </c>
+      <c r="AV134">
+        <v>8</v>
+      </c>
+      <c r="AW134">
+        <v>11</v>
+      </c>
+      <c r="AX134">
+        <v>10</v>
+      </c>
+      <c r="AY134">
+        <v>15</v>
+      </c>
+      <c r="AZ134">
+        <v>18</v>
+      </c>
+      <c r="BA134">
+        <v>8</v>
+      </c>
+      <c r="BB134">
+        <v>5</v>
+      </c>
+      <c r="BC134">
+        <v>13</v>
+      </c>
+      <c r="BD134">
+        <v>0</v>
+      </c>
+      <c r="BE134">
+        <v>0</v>
+      </c>
+      <c r="BF134">
+        <v>0</v>
+      </c>
+      <c r="BG134">
+        <v>0</v>
+      </c>
+      <c r="BH134">
+        <v>0</v>
+      </c>
+      <c r="BI134">
+        <v>0</v>
+      </c>
+      <c r="BJ134">
+        <v>0</v>
+      </c>
+      <c r="BK134">
+        <v>0</v>
+      </c>
+      <c r="BL134">
+        <v>0</v>
+      </c>
+      <c r="BM134">
+        <v>0</v>
+      </c>
+      <c r="BN134">
+        <v>0</v>
+      </c>
+      <c r="BO134">
+        <v>0</v>
+      </c>
+      <c r="BP134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7480272</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45668.5</v>
+      </c>
+      <c r="F135">
+        <v>23</v>
+      </c>
+      <c r="G135" t="s">
+        <v>79</v>
+      </c>
+      <c r="H135" t="s">
+        <v>71</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135">
+        <v>3</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>4</v>
+      </c>
+      <c r="O135" t="s">
+        <v>186</v>
+      </c>
+      <c r="P135" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q135">
+        <v>2.35</v>
+      </c>
+      <c r="R135">
+        <v>2.15</v>
+      </c>
+      <c r="S135">
+        <v>4.33</v>
+      </c>
+      <c r="T135">
+        <v>1.38</v>
+      </c>
+      <c r="U135">
+        <v>2.8</v>
+      </c>
+      <c r="V135">
+        <v>2.7</v>
+      </c>
+      <c r="W135">
+        <v>1.4</v>
+      </c>
+      <c r="X135">
+        <v>7</v>
+      </c>
+      <c r="Y135">
+        <v>1.09</v>
+      </c>
+      <c r="Z135">
+        <v>1.53</v>
+      </c>
+      <c r="AA135">
+        <v>4.4</v>
+      </c>
+      <c r="AB135">
+        <v>5.75</v>
+      </c>
+      <c r="AC135">
+        <v>1.05</v>
+      </c>
+      <c r="AD135">
+        <v>9.5</v>
+      </c>
+      <c r="AE135">
+        <v>1.28</v>
+      </c>
+      <c r="AF135">
+        <v>3.55</v>
+      </c>
+      <c r="AG135">
+        <v>1.77</v>
+      </c>
+      <c r="AH135">
+        <v>1.98</v>
+      </c>
+      <c r="AI135">
+        <v>1.8</v>
+      </c>
+      <c r="AJ135">
+        <v>1.88</v>
+      </c>
+      <c r="AK135">
+        <v>1.22</v>
+      </c>
+      <c r="AL135">
+        <v>1.27</v>
+      </c>
+      <c r="AM135">
+        <v>1.95</v>
+      </c>
+      <c r="AN135">
+        <v>1.27</v>
+      </c>
+      <c r="AO135">
+        <v>1.18</v>
+      </c>
+      <c r="AP135">
+        <v>1.42</v>
+      </c>
+      <c r="AQ135">
+        <v>1.08</v>
+      </c>
+      <c r="AR135">
+        <v>1.42</v>
+      </c>
+      <c r="AS135">
+        <v>1.15</v>
+      </c>
+      <c r="AT135">
+        <v>2.57</v>
+      </c>
+      <c r="AU135">
+        <v>5</v>
+      </c>
+      <c r="AV135">
+        <v>3</v>
+      </c>
+      <c r="AW135">
+        <v>4</v>
+      </c>
+      <c r="AX135">
+        <v>2</v>
+      </c>
+      <c r="AY135">
+        <v>9</v>
+      </c>
+      <c r="AZ135">
+        <v>5</v>
+      </c>
+      <c r="BA135">
+        <v>3</v>
+      </c>
+      <c r="BB135">
+        <v>6</v>
+      </c>
+      <c r="BC135">
+        <v>9</v>
+      </c>
+      <c r="BD135">
+        <v>0</v>
+      </c>
+      <c r="BE135">
+        <v>0</v>
+      </c>
+      <c r="BF135">
+        <v>0</v>
+      </c>
+      <c r="BG135">
+        <v>0</v>
+      </c>
+      <c r="BH135">
+        <v>0</v>
+      </c>
+      <c r="BI135">
+        <v>0</v>
+      </c>
+      <c r="BJ135">
+        <v>0</v>
+      </c>
+      <c r="BK135">
+        <v>0</v>
+      </c>
+      <c r="BL135">
+        <v>0</v>
+      </c>
+      <c r="BM135">
+        <v>0</v>
+      </c>
+      <c r="BN135">
+        <v>0</v>
+      </c>
+      <c r="BO135">
+        <v>0</v>
+      </c>
+      <c r="BP135">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="261">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -577,6 +577,9 @@
     <t>['27', '30', '81']</t>
   </si>
   <si>
+    <t>['16', '20', '25']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -791,6 +794,9 @@
   </si>
   <si>
     <t>['40', '81', '90+6', '90+8']</t>
+  </si>
+  <si>
+    <t>['54']</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1820,7 +1826,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2438,7 +2444,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2722,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ8">
         <v>1.08</v>
@@ -2850,7 +2856,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3137,7 +3143,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ10">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3262,7 +3268,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3468,7 +3474,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3546,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
         <v>0.91</v>
@@ -3674,7 +3680,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3755,7 +3761,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ13">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3961,7 +3967,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ14">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR14">
         <v>2.04</v>
@@ -4086,7 +4092,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4370,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
@@ -4498,7 +4504,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4785,7 +4791,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ18">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
         <v>1.47</v>
@@ -4988,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ19">
         <v>0.75</v>
@@ -5116,7 +5122,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5322,7 +5328,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5528,7 +5534,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5940,7 +5946,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6146,7 +6152,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6430,7 +6436,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
         <v>1.08</v>
@@ -6639,7 +6645,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ27">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
         <v>2.21</v>
@@ -6845,7 +6851,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ28">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR28">
         <v>0.85</v>
@@ -7176,7 +7182,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7588,7 +7594,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7669,7 +7675,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -7875,7 +7881,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
         <v>0.87</v>
@@ -8000,7 +8006,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8206,7 +8212,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8412,7 +8418,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8618,7 +8624,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8824,7 +8830,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9108,7 +9114,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ39">
         <v>1.09</v>
@@ -9236,7 +9242,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9442,7 +9448,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9648,7 +9654,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9854,7 +9860,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10060,7 +10066,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10138,10 +10144,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ44">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10344,10 +10350,10 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ45">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR45">
         <v>1.85</v>
@@ -10472,7 +10478,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10678,7 +10684,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11090,7 +11096,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11708,7 +11714,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11789,7 +11795,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ52">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -11914,7 +11920,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12198,7 +12204,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ54">
         <v>1.58</v>
@@ -12407,7 +12413,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ55">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR55">
         <v>1.27</v>
@@ -12532,7 +12538,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12738,7 +12744,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12816,7 +12822,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ57">
         <v>0.91</v>
@@ -12944,7 +12950,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13356,7 +13362,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13437,7 +13443,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ60">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR60">
         <v>1.06</v>
@@ -13562,7 +13568,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13974,7 +13980,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14052,7 +14058,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ63">
         <v>1.18</v>
@@ -14180,7 +14186,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14261,7 +14267,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ64">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14592,7 +14598,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14798,7 +14804,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15210,7 +15216,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15416,7 +15422,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15497,7 +15503,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ70">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR70">
         <v>1.19</v>
@@ -15622,7 +15628,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15700,7 +15706,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ71">
         <v>1.09</v>
@@ -15828,7 +15834,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16112,10 +16118,10 @@
         <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ73">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16446,7 +16452,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16730,7 +16736,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ76">
         <v>1.58</v>
@@ -16858,7 +16864,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17064,7 +17070,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17270,7 +17276,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17476,7 +17482,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18094,7 +18100,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18300,7 +18306,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18506,7 +18512,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18712,7 +18718,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18996,7 +19002,7 @@
         <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ87">
         <v>0.75</v>
@@ -19124,7 +19130,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19330,7 +19336,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19408,7 +19414,7 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ89">
         <v>2.55</v>
@@ -19820,10 +19826,10 @@
         <v>0.88</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ91">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
         <v>1.37</v>
@@ -20566,7 +20572,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20772,7 +20778,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20978,7 +20984,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21184,7 +21190,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21471,7 +21477,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ99">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21596,7 +21602,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21802,7 +21808,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22086,7 +22092,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ102">
         <v>1.09</v>
@@ -22214,7 +22220,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22292,7 +22298,7 @@
         <v>0.63</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ103">
         <v>1.09</v>
@@ -22707,7 +22713,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR105">
         <v>1.69</v>
@@ -22832,7 +22838,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23244,7 +23250,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23656,7 +23662,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24068,7 +24074,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24149,7 +24155,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR112">
         <v>1.24</v>
@@ -24355,7 +24361,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ113">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24686,7 +24692,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24892,7 +24898,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -26000,7 +26006,7 @@
         <v>2.78</v>
       </c>
       <c r="AP121">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ121">
         <v>2.55</v>
@@ -26128,7 +26134,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26206,7 +26212,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ122">
         <v>1.09</v>
@@ -26334,7 +26340,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26540,7 +26546,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -27158,7 +27164,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27239,7 +27245,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR127">
         <v>1.36</v>
@@ -27364,7 +27370,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27570,7 +27576,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28281,22 +28287,22 @@
         <v>3.11</v>
       </c>
       <c r="AU132">
+        <v>3</v>
+      </c>
+      <c r="AV132">
         <v>4</v>
       </c>
-      <c r="AV132">
-        <v>5</v>
-      </c>
       <c r="AW132">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX132">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY132">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ132">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA132">
         <v>3</v>
@@ -28394,7 +28400,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28490,19 +28496,19 @@
         <v>2</v>
       </c>
       <c r="AV133">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX133">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AY133">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ133">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -28693,19 +28699,19 @@
         <v>2.43</v>
       </c>
       <c r="AU134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV134">
         <v>8</v>
       </c>
       <c r="AW134">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX134">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY134">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ134">
         <v>18</v>
@@ -28806,7 +28812,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -28899,13 +28905,13 @@
         <v>2.57</v>
       </c>
       <c r="AU135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV135">
         <v>3</v>
       </c>
       <c r="AW135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX135">
         <v>2</v>
@@ -28963,6 +28969,418 @@
       </c>
       <c r="BP135">
         <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7480273</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45669.5</v>
+      </c>
+      <c r="F136">
+        <v>23</v>
+      </c>
+      <c r="G136" t="s">
+        <v>76</v>
+      </c>
+      <c r="H136" t="s">
+        <v>75</v>
+      </c>
+      <c r="I136">
+        <v>3</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>3</v>
+      </c>
+      <c r="L136">
+        <v>3</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>4</v>
+      </c>
+      <c r="O136" t="s">
+        <v>187</v>
+      </c>
+      <c r="P136" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q136">
+        <v>1.37</v>
+      </c>
+      <c r="R136">
+        <v>3.4</v>
+      </c>
+      <c r="S136">
+        <v>11.5</v>
+      </c>
+      <c r="T136">
+        <v>1.16</v>
+      </c>
+      <c r="U136">
+        <v>4.6</v>
+      </c>
+      <c r="V136">
+        <v>1.75</v>
+      </c>
+      <c r="W136">
+        <v>1.93</v>
+      </c>
+      <c r="X136">
+        <v>3.4</v>
+      </c>
+      <c r="Y136">
+        <v>1.28</v>
+      </c>
+      <c r="Z136">
+        <v>1.07</v>
+      </c>
+      <c r="AA136">
+        <v>11</v>
+      </c>
+      <c r="AB136">
+        <v>23</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>1.07</v>
+      </c>
+      <c r="AF136">
+        <v>8</v>
+      </c>
+      <c r="AG136">
+        <v>1.33</v>
+      </c>
+      <c r="AH136">
+        <v>3</v>
+      </c>
+      <c r="AI136">
+        <v>2.1</v>
+      </c>
+      <c r="AJ136">
+        <v>1.63</v>
+      </c>
+      <c r="AK136">
+        <v>1.01</v>
+      </c>
+      <c r="AL136">
+        <v>1.04</v>
+      </c>
+      <c r="AM136">
+        <v>7.25</v>
+      </c>
+      <c r="AN136">
+        <v>2.8</v>
+      </c>
+      <c r="AO136">
+        <v>0.73</v>
+      </c>
+      <c r="AP136">
+        <v>2.82</v>
+      </c>
+      <c r="AQ136">
+        <v>0.67</v>
+      </c>
+      <c r="AR136">
+        <v>2.05</v>
+      </c>
+      <c r="AS136">
+        <v>1.03</v>
+      </c>
+      <c r="AT136">
+        <v>3.08</v>
+      </c>
+      <c r="AU136">
+        <v>7</v>
+      </c>
+      <c r="AV136">
+        <v>3</v>
+      </c>
+      <c r="AW136">
+        <v>2</v>
+      </c>
+      <c r="AX136">
+        <v>2</v>
+      </c>
+      <c r="AY136">
+        <v>23</v>
+      </c>
+      <c r="AZ136">
+        <v>9</v>
+      </c>
+      <c r="BA136">
+        <v>12</v>
+      </c>
+      <c r="BB136">
+        <v>2</v>
+      </c>
+      <c r="BC136">
+        <v>14</v>
+      </c>
+      <c r="BD136">
+        <v>0</v>
+      </c>
+      <c r="BE136">
+        <v>0</v>
+      </c>
+      <c r="BF136">
+        <v>0</v>
+      </c>
+      <c r="BG136">
+        <v>0</v>
+      </c>
+      <c r="BH136">
+        <v>0</v>
+      </c>
+      <c r="BI136">
+        <v>0</v>
+      </c>
+      <c r="BJ136">
+        <v>0</v>
+      </c>
+      <c r="BK136">
+        <v>0</v>
+      </c>
+      <c r="BL136">
+        <v>0</v>
+      </c>
+      <c r="BM136">
+        <v>0</v>
+      </c>
+      <c r="BN136">
+        <v>0</v>
+      </c>
+      <c r="BO136">
+        <v>0</v>
+      </c>
+      <c r="BP136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7480270</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45669.5</v>
+      </c>
+      <c r="F137">
+        <v>23</v>
+      </c>
+      <c r="G137" t="s">
+        <v>80</v>
+      </c>
+      <c r="H137" t="s">
+        <v>70</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137" t="s">
+        <v>82</v>
+      </c>
+      <c r="P137" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q137">
+        <v>2.75</v>
+      </c>
+      <c r="R137">
+        <v>2.15</v>
+      </c>
+      <c r="S137">
+        <v>3.4</v>
+      </c>
+      <c r="T137">
+        <v>1.35</v>
+      </c>
+      <c r="U137">
+        <v>2.95</v>
+      </c>
+      <c r="V137">
+        <v>2.55</v>
+      </c>
+      <c r="W137">
+        <v>1.44</v>
+      </c>
+      <c r="X137">
+        <v>6.25</v>
+      </c>
+      <c r="Y137">
+        <v>1.1</v>
+      </c>
+      <c r="Z137">
+        <v>2.45</v>
+      </c>
+      <c r="AA137">
+        <v>3.3</v>
+      </c>
+      <c r="AB137">
+        <v>2.8</v>
+      </c>
+      <c r="AC137">
+        <v>1.05</v>
+      </c>
+      <c r="AD137">
+        <v>9.5</v>
+      </c>
+      <c r="AE137">
+        <v>1.25</v>
+      </c>
+      <c r="AF137">
+        <v>3.7</v>
+      </c>
+      <c r="AG137">
+        <v>1.75</v>
+      </c>
+      <c r="AH137">
+        <v>1.95</v>
+      </c>
+      <c r="AI137">
+        <v>1.63</v>
+      </c>
+      <c r="AJ137">
+        <v>2.1</v>
+      </c>
+      <c r="AK137">
+        <v>1.38</v>
+      </c>
+      <c r="AL137">
+        <v>1.29</v>
+      </c>
+      <c r="AM137">
+        <v>1.6</v>
+      </c>
+      <c r="AN137">
+        <v>2</v>
+      </c>
+      <c r="AO137">
+        <v>0.73</v>
+      </c>
+      <c r="AP137">
+        <v>1.92</v>
+      </c>
+      <c r="AQ137">
+        <v>0.75</v>
+      </c>
+      <c r="AR137">
+        <v>1.38</v>
+      </c>
+      <c r="AS137">
+        <v>1.16</v>
+      </c>
+      <c r="AT137">
+        <v>2.54</v>
+      </c>
+      <c r="AU137">
+        <v>2</v>
+      </c>
+      <c r="AV137">
+        <v>3</v>
+      </c>
+      <c r="AW137">
+        <v>6</v>
+      </c>
+      <c r="AX137">
+        <v>4</v>
+      </c>
+      <c r="AY137">
+        <v>10</v>
+      </c>
+      <c r="AZ137">
+        <v>10</v>
+      </c>
+      <c r="BA137">
+        <v>4</v>
+      </c>
+      <c r="BB137">
+        <v>3</v>
+      </c>
+      <c r="BC137">
+        <v>7</v>
+      </c>
+      <c r="BD137">
+        <v>1.84</v>
+      </c>
+      <c r="BE137">
+        <v>6.75</v>
+      </c>
+      <c r="BF137">
+        <v>2.12</v>
+      </c>
+      <c r="BG137">
+        <v>1.17</v>
+      </c>
+      <c r="BH137">
+        <v>4.35</v>
+      </c>
+      <c r="BI137">
+        <v>1.3</v>
+      </c>
+      <c r="BJ137">
+        <v>3.15</v>
+      </c>
+      <c r="BK137">
+        <v>1.5</v>
+      </c>
+      <c r="BL137">
+        <v>2.38</v>
+      </c>
+      <c r="BM137">
+        <v>1.8</v>
+      </c>
+      <c r="BN137">
+        <v>1.89</v>
+      </c>
+      <c r="BO137">
+        <v>2.23</v>
+      </c>
+      <c r="BP137">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="263">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -580,6 +580,9 @@
     <t>['16', '20', '25']</t>
   </si>
   <si>
+    <t>['41', '54', '78']</t>
+  </si>
+  <si>
     <t>['18', '79']</t>
   </si>
   <si>
@@ -797,6 +800,9 @@
   </si>
   <si>
     <t>['54']</t>
+  </si>
+  <si>
+    <t>['5', '53', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1826,7 +1832,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2444,7 +2450,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2856,7 +2862,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3140,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
         <v>0.75</v>
@@ -3268,7 +3274,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3349,7 +3355,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ11">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3474,7 +3480,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3680,7 +3686,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4092,7 +4098,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4504,7 +4510,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -4585,7 +4591,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ17">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR17">
         <v>1.07</v>
@@ -5122,7 +5128,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5200,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20">
         <v>0.91</v>
@@ -5328,7 +5334,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5534,7 +5540,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5946,7 +5952,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6152,7 +6158,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -7182,7 +7188,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7594,7 +7600,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8006,7 +8012,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8212,7 +8218,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8418,7 +8424,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8624,7 +8630,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8702,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>1.2</v>
@@ -8830,7 +8836,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -8911,7 +8917,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ38">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR38">
         <v>1.42</v>
@@ -9242,7 +9248,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9448,7 +9454,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9654,7 +9660,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9732,7 +9738,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42">
         <v>0.75</v>
@@ -9860,7 +9866,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -9941,7 +9947,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ43">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR43">
         <v>1.4</v>
@@ -10066,7 +10072,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10478,7 +10484,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10684,7 +10690,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11096,7 +11102,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11714,7 +11720,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11792,7 +11798,7 @@
         <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52">
         <v>0.67</v>
@@ -11920,7 +11926,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12538,7 +12544,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12619,7 +12625,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ56">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12744,7 +12750,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12950,7 +12956,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13362,7 +13368,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13568,7 +13574,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13980,7 +13986,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14186,7 +14192,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14598,7 +14604,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14676,7 +14682,7 @@
         <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ66">
         <v>0.75</v>
@@ -14804,7 +14810,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15216,7 +15222,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15422,7 +15428,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15628,7 +15634,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15834,7 +15840,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15915,7 +15921,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16452,7 +16458,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16864,7 +16870,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -17070,7 +17076,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17148,7 +17154,7 @@
         <v>0.4</v>
       </c>
       <c r="AP78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ78">
         <v>1.09</v>
@@ -17276,7 +17282,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17357,7 +17363,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ79">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR79">
         <v>1.56</v>
@@ -17482,7 +17488,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18100,7 +18106,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18306,7 +18312,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18512,7 +18518,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18718,7 +18724,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -19130,7 +19136,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19208,7 +19214,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
         <v>1.08</v>
@@ -19336,7 +19342,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -19417,7 +19423,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ89">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -20572,7 +20578,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20778,7 +20784,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20984,7 +20990,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21190,7 +21196,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21602,7 +21608,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21808,7 +21814,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22220,7 +22226,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22507,7 +22513,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR104">
         <v>1.42</v>
@@ -22838,7 +22844,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23250,7 +23256,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23328,7 +23334,7 @@
         <v>0.38</v>
       </c>
       <c r="AP108">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>1.09</v>
@@ -23662,7 +23668,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24074,7 +24080,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24692,7 +24698,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24898,7 +24904,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -26009,7 +26015,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ121">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR121">
         <v>2.04</v>
@@ -26134,7 +26140,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26340,7 +26346,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26418,7 +26424,7 @@
         <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ123">
         <v>1.58</v>
@@ -26546,7 +26552,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -27164,7 +27170,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27370,7 +27376,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27576,7 +27582,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28272,7 +28278,7 @@
         <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ132">
         <v>1.18</v>
@@ -28400,7 +28406,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28481,7 +28487,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -28812,7 +28818,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29018,7 +29024,7 @@
         <v>187</v>
       </c>
       <c r="P136" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q136">
         <v>1.37</v>
@@ -29381,6 +29387,212 @@
       </c>
       <c r="BP137">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7480234</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45671.70833333334</v>
+      </c>
+      <c r="F138">
+        <v>17</v>
+      </c>
+      <c r="G138" t="s">
+        <v>78</v>
+      </c>
+      <c r="H138" t="s">
+        <v>74</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>2</v>
+      </c>
+      <c r="L138">
+        <v>3</v>
+      </c>
+      <c r="M138">
+        <v>3</v>
+      </c>
+      <c r="N138">
+        <v>6</v>
+      </c>
+      <c r="O138" t="s">
+        <v>188</v>
+      </c>
+      <c r="P138" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q138">
+        <v>10</v>
+      </c>
+      <c r="R138">
+        <v>3</v>
+      </c>
+      <c r="S138">
+        <v>1.57</v>
+      </c>
+      <c r="T138">
+        <v>1.22</v>
+      </c>
+      <c r="U138">
+        <v>4</v>
+      </c>
+      <c r="V138">
+        <v>2</v>
+      </c>
+      <c r="W138">
+        <v>1.73</v>
+      </c>
+      <c r="X138">
+        <v>4.33</v>
+      </c>
+      <c r="Y138">
+        <v>1.2</v>
+      </c>
+      <c r="Z138">
+        <v>9.5</v>
+      </c>
+      <c r="AA138">
+        <v>5.5</v>
+      </c>
+      <c r="AB138">
+        <v>1.29</v>
+      </c>
+      <c r="AC138">
+        <v>1.01</v>
+      </c>
+      <c r="AD138">
+        <v>17</v>
+      </c>
+      <c r="AE138">
+        <v>1.12</v>
+      </c>
+      <c r="AF138">
+        <v>6</v>
+      </c>
+      <c r="AG138">
+        <v>1.55</v>
+      </c>
+      <c r="AH138">
+        <v>2.25</v>
+      </c>
+      <c r="AI138">
+        <v>1.95</v>
+      </c>
+      <c r="AJ138">
+        <v>1.8</v>
+      </c>
+      <c r="AK138">
+        <v>4.33</v>
+      </c>
+      <c r="AL138">
+        <v>1.1</v>
+      </c>
+      <c r="AM138">
+        <v>1.04</v>
+      </c>
+      <c r="AN138">
+        <v>1.27</v>
+      </c>
+      <c r="AO138">
+        <v>2.55</v>
+      </c>
+      <c r="AP138">
+        <v>1.25</v>
+      </c>
+      <c r="AQ138">
+        <v>2.42</v>
+      </c>
+      <c r="AR138">
+        <v>1.32</v>
+      </c>
+      <c r="AS138">
+        <v>1.86</v>
+      </c>
+      <c r="AT138">
+        <v>3.18</v>
+      </c>
+      <c r="AU138">
+        <v>6</v>
+      </c>
+      <c r="AV138">
+        <v>5</v>
+      </c>
+      <c r="AW138">
+        <v>2</v>
+      </c>
+      <c r="AX138">
+        <v>6</v>
+      </c>
+      <c r="AY138">
+        <v>8</v>
+      </c>
+      <c r="AZ138">
+        <v>13</v>
+      </c>
+      <c r="BA138">
+        <v>2</v>
+      </c>
+      <c r="BB138">
+        <v>4</v>
+      </c>
+      <c r="BC138">
+        <v>6</v>
+      </c>
+      <c r="BD138">
+        <v>5.8</v>
+      </c>
+      <c r="BE138">
+        <v>10.5</v>
+      </c>
+      <c r="BF138">
+        <v>1.13</v>
+      </c>
+      <c r="BG138">
+        <v>1.13</v>
+      </c>
+      <c r="BH138">
+        <v>4.9</v>
+      </c>
+      <c r="BI138">
+        <v>1.23</v>
+      </c>
+      <c r="BJ138">
+        <v>3.65</v>
+      </c>
+      <c r="BK138">
+        <v>1.38</v>
+      </c>
+      <c r="BL138">
+        <v>2.7</v>
+      </c>
+      <c r="BM138">
+        <v>1.61</v>
+      </c>
+      <c r="BN138">
+        <v>2.15</v>
+      </c>
+      <c r="BO138">
+        <v>1.95</v>
+      </c>
+      <c r="BP138">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -581,6 +581,9 @@
   </si>
   <si>
     <t>['41', '54', '78']</t>
+  </si>
+  <si>
+    <t>['13', '90+3', '90+7']</t>
   </si>
   <si>
     <t>['18', '79']</t>
@@ -1164,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP138"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1832,7 +1835,7 @@
         <v>83</v>
       </c>
       <c r="P4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2450,7 +2453,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q7">
         <v>3.6</v>
@@ -2531,7 +2534,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2734,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ8">
         <v>1.08</v>
@@ -2862,7 +2865,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -3274,7 +3277,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3480,7 +3483,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3686,7 +3689,7 @@
         <v>82</v>
       </c>
       <c r="P13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -4098,7 +4101,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
@@ -4382,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
@@ -4510,7 +4513,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -5128,7 +5131,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -5334,7 +5337,7 @@
         <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5540,7 +5543,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5621,7 +5624,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR22">
         <v>1.66</v>
@@ -5952,7 +5955,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
@@ -6158,7 +6161,7 @@
         <v>99</v>
       </c>
       <c r="P25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -7188,7 +7191,7 @@
         <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7600,7 +7603,7 @@
         <v>105</v>
       </c>
       <c r="P32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8012,7 +8015,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8218,7 +8221,7 @@
         <v>108</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8424,7 +8427,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8630,7 +8633,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8711,7 +8714,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -8836,7 +8839,7 @@
         <v>82</v>
       </c>
       <c r="P38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -9120,7 +9123,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ39">
         <v>1.09</v>
@@ -9248,7 +9251,7 @@
         <v>82</v>
       </c>
       <c r="P40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9454,7 +9457,7 @@
         <v>112</v>
       </c>
       <c r="P41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9660,7 +9663,7 @@
         <v>113</v>
       </c>
       <c r="P42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9866,7 +9869,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>9.5</v>
@@ -10072,7 +10075,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10356,7 +10359,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ45">
         <v>0.67</v>
@@ -10484,7 +10487,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q46">
         <v>1.67</v>
@@ -10565,7 +10568,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
         <v>2.16</v>
@@ -10690,7 +10693,7 @@
         <v>118</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11102,7 +11105,7 @@
         <v>82</v>
       </c>
       <c r="P49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q49">
         <v>2.63</v>
@@ -11720,7 +11723,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11926,7 +11929,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q53">
         <v>3.75</v>
@@ -12544,7 +12547,7 @@
         <v>82</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q56">
         <v>7.5</v>
@@ -12750,7 +12753,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -12828,7 +12831,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ57">
         <v>0.91</v>
@@ -12956,7 +12959,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q58">
         <v>2.4</v>
@@ -13368,7 +13371,7 @@
         <v>128</v>
       </c>
       <c r="P60" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q60">
         <v>2.38</v>
@@ -13574,7 +13577,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13986,7 +13989,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63">
         <v>4.33</v>
@@ -14192,7 +14195,7 @@
         <v>132</v>
       </c>
       <c r="P64" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -14604,7 +14607,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -14810,7 +14813,7 @@
         <v>134</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67">
         <v>2.4</v>
@@ -15222,7 +15225,7 @@
         <v>136</v>
       </c>
       <c r="P69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15428,7 +15431,7 @@
         <v>137</v>
       </c>
       <c r="P70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q70">
         <v>2.5</v>
@@ -15634,7 +15637,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>2.25</v>
@@ -15840,7 +15843,7 @@
         <v>82</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16124,7 +16127,7 @@
         <v>0.57</v>
       </c>
       <c r="AP73">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ73">
         <v>0.75</v>
@@ -16458,7 +16461,7 @@
         <v>141</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16742,7 +16745,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ76">
         <v>1.58</v>
@@ -16870,7 +16873,7 @@
         <v>143</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16951,7 +16954,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ77">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR77">
         <v>1.13</v>
@@ -17076,7 +17079,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
@@ -17282,7 +17285,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17488,7 +17491,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17569,7 +17572,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ80">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR80">
         <v>1.33</v>
@@ -18106,7 +18109,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18312,7 +18315,7 @@
         <v>82</v>
       </c>
       <c r="P84" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q84">
         <v>3.25</v>
@@ -18518,7 +18521,7 @@
         <v>82</v>
       </c>
       <c r="P85" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>7.5</v>
@@ -18724,7 +18727,7 @@
         <v>150</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>2.88</v>
@@ -18805,7 +18808,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19008,7 +19011,7 @@
         <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ87">
         <v>0.75</v>
@@ -19136,7 +19139,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19342,7 +19345,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q89">
         <v>6</v>
@@ -20578,7 +20581,7 @@
         <v>82</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q95">
         <v>10</v>
@@ -20784,7 +20787,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20990,7 +20993,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -21196,7 +21199,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21608,7 +21611,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21814,7 +21817,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22098,7 +22101,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ102">
         <v>1.09</v>
@@ -22226,7 +22229,7 @@
         <v>163</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22844,7 +22847,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23256,7 +23259,7 @@
         <v>82</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>2.38</v>
@@ -23543,7 +23546,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ109">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR109">
         <v>1.35</v>
@@ -23668,7 +23671,7 @@
         <v>127</v>
       </c>
       <c r="P110" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24080,7 +24083,7 @@
         <v>169</v>
       </c>
       <c r="P112" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24698,7 +24701,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q115">
         <v>7</v>
@@ -24904,7 +24907,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>2.65</v>
@@ -25191,7 +25194,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ117">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR117">
         <v>1.33</v>
@@ -26012,7 +26015,7 @@
         <v>2.78</v>
       </c>
       <c r="AP121">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ121">
         <v>2.42</v>
@@ -26140,7 +26143,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q122">
         <v>2</v>
@@ -26346,7 +26349,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26552,7 +26555,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q124">
         <v>6.5</v>
@@ -26839,7 +26842,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ125">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -27170,7 +27173,7 @@
         <v>82</v>
       </c>
       <c r="P127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q127">
         <v>3</v>
@@ -27376,7 +27379,7 @@
         <v>82</v>
       </c>
       <c r="P128" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q128">
         <v>2.05</v>
@@ -27582,7 +27585,7 @@
         <v>183</v>
       </c>
       <c r="P129" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q129">
         <v>3.2</v>
@@ -28406,7 +28409,7 @@
         <v>185</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q133">
         <v>10</v>
@@ -28818,7 +28821,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q135">
         <v>2.35</v>
@@ -29024,7 +29027,7 @@
         <v>187</v>
       </c>
       <c r="P136" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q136">
         <v>1.37</v>
@@ -29102,7 +29105,7 @@
         <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ136">
         <v>0.67</v>
@@ -29436,7 +29439,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q138">
         <v>10</v>
@@ -29593,6 +29596,212 @@
       </c>
       <c r="BP138">
         <v>1.75</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7480238</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45672.70833333334</v>
+      </c>
+      <c r="F139">
+        <v>17</v>
+      </c>
+      <c r="G139" t="s">
+        <v>76</v>
+      </c>
+      <c r="H139" t="s">
+        <v>80</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>3</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>3</v>
+      </c>
+      <c r="O139" t="s">
+        <v>189</v>
+      </c>
+      <c r="P139" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q139">
+        <v>1.91</v>
+      </c>
+      <c r="R139">
+        <v>2.5</v>
+      </c>
+      <c r="S139">
+        <v>6.5</v>
+      </c>
+      <c r="T139">
+        <v>1.3</v>
+      </c>
+      <c r="U139">
+        <v>3.4</v>
+      </c>
+      <c r="V139">
+        <v>2.5</v>
+      </c>
+      <c r="W139">
+        <v>1.5</v>
+      </c>
+      <c r="X139">
+        <v>6</v>
+      </c>
+      <c r="Y139">
+        <v>1.13</v>
+      </c>
+      <c r="Z139">
+        <v>1.25</v>
+      </c>
+      <c r="AA139">
+        <v>5.3</v>
+      </c>
+      <c r="AB139">
+        <v>7.4</v>
+      </c>
+      <c r="AC139">
+        <v>1.02</v>
+      </c>
+      <c r="AD139">
+        <v>15</v>
+      </c>
+      <c r="AE139">
+        <v>1.12</v>
+      </c>
+      <c r="AF139">
+        <v>6.5</v>
+      </c>
+      <c r="AG139">
+        <v>1.4</v>
+      </c>
+      <c r="AH139">
+        <v>2.75</v>
+      </c>
+      <c r="AI139">
+        <v>1.91</v>
+      </c>
+      <c r="AJ139">
+        <v>1.91</v>
+      </c>
+      <c r="AK139">
+        <v>1.04</v>
+      </c>
+      <c r="AL139">
+        <v>1.09</v>
+      </c>
+      <c r="AM139">
+        <v>3.7</v>
+      </c>
+      <c r="AN139">
+        <v>2.82</v>
+      </c>
+      <c r="AO139">
+        <v>1.2</v>
+      </c>
+      <c r="AP139">
+        <v>2.83</v>
+      </c>
+      <c r="AQ139">
+        <v>1.09</v>
+      </c>
+      <c r="AR139">
+        <v>2</v>
+      </c>
+      <c r="AS139">
+        <v>1.2</v>
+      </c>
+      <c r="AT139">
+        <v>3.2</v>
+      </c>
+      <c r="AU139">
+        <v>13</v>
+      </c>
+      <c r="AV139">
+        <v>3</v>
+      </c>
+      <c r="AW139">
+        <v>19</v>
+      </c>
+      <c r="AX139">
+        <v>3</v>
+      </c>
+      <c r="AY139">
+        <v>37</v>
+      </c>
+      <c r="AZ139">
+        <v>7</v>
+      </c>
+      <c r="BA139">
+        <v>10</v>
+      </c>
+      <c r="BB139">
+        <v>3</v>
+      </c>
+      <c r="BC139">
+        <v>13</v>
+      </c>
+      <c r="BD139">
+        <v>1.24</v>
+      </c>
+      <c r="BE139">
+        <v>8.5</v>
+      </c>
+      <c r="BF139">
+        <v>4.1</v>
+      </c>
+      <c r="BG139">
+        <v>1.11</v>
+      </c>
+      <c r="BH139">
+        <v>5.3</v>
+      </c>
+      <c r="BI139">
+        <v>1.21</v>
+      </c>
+      <c r="BJ139">
+        <v>3.8</v>
+      </c>
+      <c r="BK139">
+        <v>1.36</v>
+      </c>
+      <c r="BL139">
+        <v>2.8</v>
+      </c>
+      <c r="BM139">
+        <v>1.58</v>
+      </c>
+      <c r="BN139">
+        <v>2.18</v>
+      </c>
+      <c r="BO139">
+        <v>1.88</v>
+      </c>
+      <c r="BP139">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
@@ -1501,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ2">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ3">
         <v>1.09</v>
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ4">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ5">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ6">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ7">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2731,25 +2731,25 @@
         <v>4.33</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ8">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2937,25 +2937,25 @@
         <v>1.5</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ9">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU9">
         <v>6</v>
@@ -3143,25 +3143,25 @@
         <v>1.36</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ10">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AU10">
         <v>8</v>
@@ -3352,22 +3352,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ11">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AU11">
         <v>0</v>
@@ -3555,25 +3555,25 @@
         <v>1.95</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ12">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AU12">
         <v>4</v>
@@ -3767,19 +3767,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU13">
         <v>3</v>
@@ -3970,22 +3970,22 @@
         <v>1</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP14">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR14">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="AS14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AT14">
-        <v>3.54</v>
+        <v>2.98</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4176,22 +4176,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ15">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="AS15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AT15">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="AU15">
         <v>3</v>
@@ -4379,25 +4379,25 @@
         <v>4.5</v>
       </c>
       <c r="AN16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO16">
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
       </c>
       <c r="AR16">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AS16">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AT16">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="AU16">
         <v>10</v>
@@ -4585,25 +4585,25 @@
         <v>1.02</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR17">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AS17">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AT17">
-        <v>2.72</v>
+        <v>3.53</v>
       </c>
       <c r="AU17">
         <v>2</v>
@@ -4791,25 +4791,25 @@
         <v>1.4</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR18">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AS18">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AT18">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="AU18">
         <v>7</v>
@@ -5003,19 +5003,19 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ19">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR19">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AS19">
-        <v>0.6899999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT19">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -5203,25 +5203,25 @@
         <v>1.73</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ20">
+        <v>1.17</v>
+      </c>
+      <c r="AR20">
+        <v>1.45</v>
+      </c>
+      <c r="AS20">
         <v>0.91</v>
       </c>
-      <c r="AR20">
-        <v>1.56</v>
-      </c>
-      <c r="AS20">
-        <v>1.22</v>
-      </c>
       <c r="AT20">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="AU20">
         <v>6</v>
@@ -5409,25 +5409,25 @@
         <v>1.42</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP21">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ21">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR21">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AS21">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="AT21">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="AU21">
         <v>6</v>
@@ -5615,25 +5615,25 @@
         <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO22">
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR22">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="AS22">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AT22">
-        <v>3.43</v>
+        <v>2.46</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5824,22 +5824,22 @@
         <v>3</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ23">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR23">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="AS23">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="AT23">
-        <v>4.28</v>
+        <v>3.96</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6027,25 +6027,25 @@
         <v>2</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP24">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ24">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR24">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AS24">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT24">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="AU24">
         <v>3</v>
@@ -6236,22 +6236,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP25">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR25">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AS25">
-        <v>1.47</v>
+        <v>1.06</v>
       </c>
       <c r="AT25">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6442,22 +6442,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP26">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ26">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR26">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AS26">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AT26">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6648,22 +6648,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP27">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR27">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AS27">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AT27">
-        <v>3.36</v>
+        <v>3.19</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6854,22 +6854,22 @@
         <v>0.5</v>
       </c>
       <c r="AO28">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP28">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ28">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR28">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="AS28">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT28">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7060,22 +7060,22 @@
         <v>0.5</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP29">
+        <v>1.09</v>
+      </c>
+      <c r="AQ29">
+        <v>1.17</v>
+      </c>
+      <c r="AR29">
         <v>1.08</v>
       </c>
-      <c r="AQ29">
-        <v>1.09</v>
-      </c>
-      <c r="AR29">
-        <v>1.33</v>
-      </c>
       <c r="AS29">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AT29">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7263,25 +7263,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP30">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR30">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="AS30">
-        <v>0.85</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7472,22 +7472,22 @@
         <v>2</v>
       </c>
       <c r="AO31">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP31">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ31">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR31">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AS31">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AT31">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="AU31">
         <v>0</v>
@@ -7675,25 +7675,25 @@
         <v>1.75</v>
       </c>
       <c r="AN32">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR32">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AS32">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AT32">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AU32">
         <v>7</v>
@@ -7881,25 +7881,25 @@
         <v>1.41</v>
       </c>
       <c r="AN33">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO33">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR33">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="AS33">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AT33">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AU33">
         <v>3</v>
@@ -8087,25 +8087,25 @@
         <v>2.25</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="AO34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ34">
         <v>1.09</v>
       </c>
       <c r="AR34">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AS34">
-        <v>0.84</v>
+        <v>1.21</v>
       </c>
       <c r="AT34">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8293,25 +8293,25 @@
         <v>1.66</v>
       </c>
       <c r="AN35">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO35">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP35">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ35">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR35">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AS35">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AT35">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8499,25 +8499,25 @@
         <v>1.58</v>
       </c>
       <c r="AN36">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO36">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP36">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ36">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AS36">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AT36">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8705,25 +8705,25 @@
         <v>1.45</v>
       </c>
       <c r="AN37">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AO37">
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR37">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS37">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT37">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8911,25 +8911,25 @@
         <v>1.04</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO38">
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ38">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR38">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="AS38">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AT38">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="AU38">
         <v>2</v>
@@ -9117,25 +9117,25 @@
         <v>2.9</v>
       </c>
       <c r="AN39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ39">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR39">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="AS39">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT39">
-        <v>3.33</v>
+        <v>2.79</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9323,25 +9323,25 @@
         <v>1.63</v>
       </c>
       <c r="AN40">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AO40">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR40">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="AS40">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AT40">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AU40">
         <v>4</v>
@@ -9529,25 +9529,25 @@
         <v>1.77</v>
       </c>
       <c r="AN41">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AO41">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP41">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ41">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR41">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS41">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT41">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9735,25 +9735,25 @@
         <v>1.62</v>
       </c>
       <c r="AN42">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO42">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR42">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AS42">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="AT42">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AU42">
         <v>4</v>
@@ -9941,25 +9941,25 @@
         <v>1.02</v>
       </c>
       <c r="AN43">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO43">
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ43">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR43">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AS43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AT43">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="AU43">
         <v>6</v>
@@ -10150,22 +10150,22 @@
         <v>3</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AP44">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR44">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AS44">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AT44">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10353,25 +10353,25 @@
         <v>5.7</v>
       </c>
       <c r="AN45">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AO45">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP45">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ45">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR45">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AS45">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AT45">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10565,19 +10565,19 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR46">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AS46">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AT46">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10765,25 +10765,25 @@
         <v>1.57</v>
       </c>
       <c r="AN47">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AO47">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AP47">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ47">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR47">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AS47">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT47">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10971,25 +10971,25 @@
         <v>2</v>
       </c>
       <c r="AN48">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AO48">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP48">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ48">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR48">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AS48">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AT48">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="AU48">
         <v>5</v>
@@ -11177,25 +11177,25 @@
         <v>1.83</v>
       </c>
       <c r="AN49">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO49">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP49">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ49">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR49">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS49">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT49">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AU49">
         <v>4</v>
@@ -11383,25 +11383,25 @@
         <v>1.5</v>
       </c>
       <c r="AN50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO50">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="AP50">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
       </c>
       <c r="AR50">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AS50">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="AT50">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AU50">
         <v>8</v>
@@ -11589,25 +11589,25 @@
         <v>1.12</v>
       </c>
       <c r="AN51">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AO51">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AP51">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ51">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR51">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AS51">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AT51">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11795,25 +11795,25 @@
         <v>2.15</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO52">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AP52">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ52">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR52">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS52">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AT52">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12001,25 +12001,25 @@
         <v>1.36</v>
       </c>
       <c r="AN53">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AO53">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP53">
+        <v>1.09</v>
+      </c>
+      <c r="AQ53">
+        <v>1.09</v>
+      </c>
+      <c r="AR53">
         <v>1.08</v>
       </c>
-      <c r="AQ53">
-        <v>0.75</v>
-      </c>
-      <c r="AR53">
-        <v>1.34</v>
-      </c>
       <c r="AS53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT53">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12207,25 +12207,25 @@
         <v>2.2</v>
       </c>
       <c r="AN54">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AP54">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ54">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR54">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS54">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT54">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU54">
         <v>6</v>
@@ -12413,25 +12413,25 @@
         <v>1.6</v>
       </c>
       <c r="AN55">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="AO55">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP55">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ55">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR55">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AS55">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AT55">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12619,25 +12619,25 @@
         <v>1.02</v>
       </c>
       <c r="AN56">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO56">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AP56">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ56">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
       </c>
       <c r="AS56">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AT56">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="AU56">
         <v>3</v>
@@ -12825,25 +12825,25 @@
         <v>4</v>
       </c>
       <c r="AN57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO57">
-        <v>0.25</v>
+        <v>0.89</v>
       </c>
       <c r="AP57">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ57">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR57">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AS57">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT57">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13031,25 +13031,25 @@
         <v>1.93</v>
       </c>
       <c r="AN58">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="AO58">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ58">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AS58">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT58">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="AU58">
         <v>6</v>
@@ -13237,25 +13237,25 @@
         <v>1.33</v>
       </c>
       <c r="AN59">
+        <v>1</v>
+      </c>
+      <c r="AO59">
+        <v>0.67</v>
+      </c>
+      <c r="AP59">
+        <v>1.09</v>
+      </c>
+      <c r="AQ59">
+        <v>1.26</v>
+      </c>
+      <c r="AR59">
+        <v>1.09</v>
+      </c>
+      <c r="AS59">
         <v>1.33</v>
       </c>
-      <c r="AO59">
-        <v>0.25</v>
-      </c>
-      <c r="AP59">
-        <v>1.08</v>
-      </c>
-      <c r="AQ59">
-        <v>1.09</v>
-      </c>
-      <c r="AR59">
-        <v>1.31</v>
-      </c>
-      <c r="AS59">
-        <v>1.36</v>
-      </c>
       <c r="AT59">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="AU59">
         <v>3</v>
@@ -13443,25 +13443,25 @@
         <v>2.05</v>
       </c>
       <c r="AN60">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO60">
+        <v>1</v>
+      </c>
+      <c r="AP60">
         <v>1.17</v>
       </c>
-      <c r="AP60">
-        <v>1.42</v>
-      </c>
       <c r="AQ60">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR60">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AS60">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AT60">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AU60">
         <v>6</v>
@@ -13649,25 +13649,25 @@
         <v>1.67</v>
       </c>
       <c r="AN61">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO61">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP61">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ61">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AS61">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT61">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13855,25 +13855,25 @@
         <v>6.25</v>
       </c>
       <c r="AN62">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AO62">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ62">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AS62">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AT62">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14061,25 +14061,25 @@
         <v>1.25</v>
       </c>
       <c r="AN63">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AO63">
-        <v>1</v>
+        <v>2.11</v>
       </c>
       <c r="AP63">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ63">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR63">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AS63">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AT63">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14267,25 +14267,25 @@
         <v>1.22</v>
       </c>
       <c r="AN64">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="AO64">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="AP64">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR64">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AS64">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14473,25 +14473,25 @@
         <v>2.05</v>
       </c>
       <c r="AN65">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO65">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
       </c>
       <c r="AR65">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AS65">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="AT65">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14679,25 +14679,25 @@
         <v>1.53</v>
       </c>
       <c r="AN66">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AO66">
+        <v>1.2</v>
+      </c>
+      <c r="AP66">
         <v>1.17</v>
       </c>
-      <c r="AP66">
-        <v>1.25</v>
-      </c>
       <c r="AQ66">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR66">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS66">
         <v>1.21</v>
       </c>
       <c r="AT66">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14885,25 +14885,25 @@
         <v>2</v>
       </c>
       <c r="AN67">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AO67">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ67">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR67">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AS67">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AT67">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15091,25 +15091,25 @@
         <v>2.05</v>
       </c>
       <c r="AN68">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO68">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ68">
         <v>1.09</v>
       </c>
       <c r="AR68">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AS68">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="AT68">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15297,25 +15297,25 @@
         <v>1.93</v>
       </c>
       <c r="AN69">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO69">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ69">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR69">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS69">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AT69">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15503,25 +15503,25 @@
         <v>1.95</v>
       </c>
       <c r="AN70">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO70">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP70">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ70">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR70">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AS70">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT70">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15709,25 +15709,25 @@
         <v>2.15</v>
       </c>
       <c r="AN71">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO71">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AP71">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ71">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR71">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS71">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AT71">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15915,25 +15915,25 @@
         <v>1.07</v>
       </c>
       <c r="AN72">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AO72">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AP72">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ72">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR72">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS72">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AT72">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16121,25 +16121,25 @@
         <v>2.88</v>
       </c>
       <c r="AN73">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="AO73">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ73">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR73">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AS73">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AT73">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16327,25 +16327,25 @@
         <v>1.36</v>
       </c>
       <c r="AN74">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="AO74">
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ74">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR74">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AS74">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AT74">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16533,25 +16533,25 @@
         <v>1.45</v>
       </c>
       <c r="AN75">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AO75">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AP75">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ75">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR75">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AS75">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AT75">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="AU75">
         <v>-1</v>
@@ -16739,25 +16739,25 @@
         <v>3.75</v>
       </c>
       <c r="AN76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO76">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AP76">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ76">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR76">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AS76">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AT76">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="AU76">
         <v>12</v>
@@ -16945,25 +16945,25 @@
         <v>1.38</v>
       </c>
       <c r="AN77">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AO77">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="AP77">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR77">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AS77">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AT77">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17151,25 +17151,25 @@
         <v>1.47</v>
       </c>
       <c r="AN78">
+        <v>1</v>
+      </c>
+      <c r="AO78">
+        <v>0.67</v>
+      </c>
+      <c r="AP78">
         <v>1.17</v>
       </c>
-      <c r="AO78">
-        <v>0.4</v>
-      </c>
-      <c r="AP78">
-        <v>1.25</v>
-      </c>
       <c r="AQ78">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR78">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AS78">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AT78">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AU78">
         <v>-1</v>
@@ -17357,25 +17357,25 @@
         <v>1.09</v>
       </c>
       <c r="AN79">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO79">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AP79">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ79">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR79">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS79">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AT79">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AU79">
         <v>-1</v>
@@ -17563,25 +17563,25 @@
         <v>1.55</v>
       </c>
       <c r="AN80">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="AO80">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="AP80">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ80">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR80">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS80">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT80">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17769,25 +17769,25 @@
         <v>7.5</v>
       </c>
       <c r="AN81">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AO81">
-        <v>0.5</v>
+        <v>1.07</v>
       </c>
       <c r="AP81">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ81">
         <v>1.09</v>
       </c>
       <c r="AR81">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AS81">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AT81">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="AU81">
         <v>10</v>
@@ -17975,25 +17975,25 @@
         <v>1.68</v>
       </c>
       <c r="AN82">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AO82">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP82">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ82">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR82">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AS82">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AT82">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18181,25 +18181,25 @@
         <v>1.8</v>
       </c>
       <c r="AN83">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AO83">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AP83">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ83">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR83">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AS83">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AT83">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18387,25 +18387,25 @@
         <v>1.53</v>
       </c>
       <c r="AN84">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AO84">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ84">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
       </c>
       <c r="AS84">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT84">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AU84">
         <v>4</v>
@@ -18593,25 +18593,25 @@
         <v>1.03</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO85">
-        <v>0.8</v>
+        <v>1.92</v>
       </c>
       <c r="AP85">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ85">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR85">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS85">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AT85">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="AU85">
         <v>2</v>
@@ -18799,25 +18799,25 @@
         <v>1.6</v>
       </c>
       <c r="AN86">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AO86">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AP86">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ86">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR86">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS86">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AT86">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -19005,25 +19005,25 @@
         <v>3.75</v>
       </c>
       <c r="AN87">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="AP87">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ87">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR87">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="AS87">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AT87">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="AU87">
         <v>12</v>
@@ -19211,25 +19211,25 @@
         <v>1.75</v>
       </c>
       <c r="AN88">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AO88">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ88">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR88">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AS88">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT88">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19417,25 +19417,25 @@
         <v>1.11</v>
       </c>
       <c r="AN89">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AO89">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AP89">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ89">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR89">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AS89">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AT89">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19623,25 +19623,25 @@
         <v>1.68</v>
       </c>
       <c r="AN90">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AO90">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AP90">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
       </c>
       <c r="AS90">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AT90">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AU90">
         <v>7</v>
@@ -19829,25 +19829,25 @@
         <v>2.4</v>
       </c>
       <c r="AN91">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AO91">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AP91">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR91">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AS91">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AT91">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -20035,25 +20035,25 @@
         <v>5.75</v>
       </c>
       <c r="AN92">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AO92">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ92">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR92">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AS92">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AT92">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="AU92">
         <v>12</v>
@@ -20241,25 +20241,25 @@
         <v>1.66</v>
       </c>
       <c r="AN93">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AO93">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="AP93">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ93">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR93">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS93">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AT93">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AU93">
         <v>8</v>
@@ -20447,25 +20447,25 @@
         <v>1.87</v>
       </c>
       <c r="AN94">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AO94">
-        <v>0.86</v>
+        <v>1.27</v>
       </c>
       <c r="AP94">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR94">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AS94">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT94">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU94">
         <v>9</v>
@@ -20653,25 +20653,25 @@
         <v>1.03</v>
       </c>
       <c r="AN95">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO95">
-        <v>1.17</v>
+        <v>2.07</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ95">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR95">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AS95">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AT95">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20859,25 +20859,25 @@
         <v>1.45</v>
       </c>
       <c r="AN96">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AO96">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP96">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ96">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR96">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT96">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21065,25 +21065,25 @@
         <v>2.45</v>
       </c>
       <c r="AN97">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AO97">
-        <v>0.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP97">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ97">
         <v>1.09</v>
       </c>
       <c r="AR97">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AS97">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="AT97">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="AU97">
         <v>8</v>
@@ -21271,25 +21271,25 @@
         <v>1.52</v>
       </c>
       <c r="AN98">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AO98">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ98">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR98">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AS98">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AT98">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21477,25 +21477,25 @@
         <v>1.35</v>
       </c>
       <c r="AN99">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP99">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ99">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR99">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS99">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AT99">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21683,25 +21683,25 @@
         <v>1.57</v>
       </c>
       <c r="AN100">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AO100">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP100">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ100">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR100">
+        <v>1.29</v>
+      </c>
+      <c r="AS100">
         <v>1.24</v>
       </c>
-      <c r="AS100">
-        <v>1.17</v>
-      </c>
       <c r="AT100">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21889,25 +21889,25 @@
         <v>1.36</v>
       </c>
       <c r="AN101">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="AO101">
-        <v>0.88</v>
+        <v>1.24</v>
       </c>
       <c r="AP101">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ101">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR101">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AS101">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT101">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22095,25 +22095,25 @@
         <v>4.5</v>
       </c>
       <c r="AN102">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="AO102">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AP102">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ102">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR102">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AS102">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AT102">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22301,25 +22301,25 @@
         <v>1.65</v>
       </c>
       <c r="AN103">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="AO103">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="AP103">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ103">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR103">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AS103">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT103">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AU103">
         <v>3</v>
@@ -22507,25 +22507,25 @@
         <v>1.01</v>
       </c>
       <c r="AN104">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ104">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR104">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AS104">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AT104">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22713,25 +22713,25 @@
         <v>2.55</v>
       </c>
       <c r="AN105">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="AO105">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="AP105">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ105">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR105">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AS105">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT105">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="AU105">
         <v>7</v>
@@ -22919,25 +22919,25 @@
         <v>1.74</v>
       </c>
       <c r="AN106">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AO106">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ106">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR106">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AS106">
         <v>1.47</v>
       </c>
       <c r="AT106">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23125,25 +23125,25 @@
         <v>6.1</v>
       </c>
       <c r="AN107">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AO107">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP107">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ107">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR107">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AS107">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AT107">
-        <v>3.59</v>
+        <v>3.32</v>
       </c>
       <c r="AU107">
         <v>8</v>
@@ -23331,25 +23331,25 @@
         <v>2</v>
       </c>
       <c r="AN108">
-        <v>1.63</v>
+        <v>1.12</v>
       </c>
       <c r="AO108">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ108">
         <v>1.09</v>
       </c>
       <c r="AR108">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AS108">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AT108">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AU108">
         <v>3</v>
@@ -23537,25 +23537,25 @@
         <v>1.48</v>
       </c>
       <c r="AN109">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO109">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AP109">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR109">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AS109">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT109">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23743,25 +23743,25 @@
         <v>1.4</v>
       </c>
       <c r="AN110">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AO110">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AP110">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ110">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR110">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AS110">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AT110">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AU110">
         <v>5</v>
@@ -23949,25 +23949,25 @@
         <v>1.08</v>
       </c>
       <c r="AN111">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AO111">
-        <v>1.43</v>
+        <v>2.19</v>
       </c>
       <c r="AP111">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ111">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR111">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AS111">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AT111">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="AU111">
         <v>4</v>
@@ -24155,25 +24155,25 @@
         <v>1.22</v>
       </c>
       <c r="AN112">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="AO112">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ112">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR112">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AS112">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AT112">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24361,25 +24361,25 @@
         <v>6.75</v>
       </c>
       <c r="AN113">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AO113">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AP113">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ113">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR113">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AS113">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AT113">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AU113">
         <v>12</v>
@@ -24570,22 +24570,22 @@
         <v>1.11</v>
       </c>
       <c r="AO114">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="AP114">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ114">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AR114">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS114">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT114">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AU114">
         <v>3</v>
@@ -24773,25 +24773,25 @@
         <v>1.07</v>
       </c>
       <c r="AN115">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AO115">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="AP115">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ115">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR115">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AS115">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AT115">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -24979,25 +24979,25 @@
         <v>1.68</v>
       </c>
       <c r="AN116">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.06</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ116">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR116">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AS116">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AT116">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AU116">
         <v>6</v>
@@ -25185,22 +25185,22 @@
         <v>1.44</v>
       </c>
       <c r="AN117">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AO117">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP117">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ117">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR117">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AS117">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AT117">
         <v>2.58</v>
@@ -25391,25 +25391,25 @@
         <v>1.73</v>
       </c>
       <c r="AN118">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AO118">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AP118">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ118">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR118">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AS118">
         <v>1.22</v>
       </c>
       <c r="AT118">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AU118">
         <v>6</v>
@@ -25597,25 +25597,25 @@
         <v>1.27</v>
       </c>
       <c r="AN119">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AO119">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ119">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AR119">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS119">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT119">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU119">
         <v>3</v>
@@ -25803,25 +25803,25 @@
         <v>1.98</v>
       </c>
       <c r="AN120">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="AO120">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AP120">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AQ120">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR120">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AS120">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AT120">
-        <v>2.87</v>
+        <v>2.57</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26009,25 +26009,25 @@
         <v>1.47</v>
       </c>
       <c r="AN121">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="AO121">
         <v>2.78</v>
       </c>
       <c r="AP121">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ121">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR121">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AS121">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AT121">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="AU121">
         <v>10</v>
@@ -26215,25 +26215,25 @@
         <v>2.5</v>
       </c>
       <c r="AN122">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AO122">
-        <v>0.67</v>
+        <v>0.95</v>
       </c>
       <c r="AP122">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ122">
         <v>1.09</v>
       </c>
       <c r="AR122">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AS122">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="AT122">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AU122">
         <v>5</v>
@@ -26421,25 +26421,25 @@
         <v>1.5</v>
       </c>
       <c r="AN123">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AO123">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AP123">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ123">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR123">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS123">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AT123">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="AU123">
         <v>5</v>
@@ -26627,25 +26627,25 @@
         <v>1.11</v>
       </c>
       <c r="AN124">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AO124">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AP124">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ124">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR124">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS124">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AT124">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26833,25 +26833,25 @@
         <v>1.47</v>
       </c>
       <c r="AN125">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AO125">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AP125">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AQ125">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR125">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AS125">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AT125">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU125">
         <v>4</v>
@@ -27039,25 +27039,25 @@
         <v>5.25</v>
       </c>
       <c r="AN126">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AO126">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP126">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ126">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AR126">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="AS126">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT126">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27245,25 +27245,25 @@
         <v>1.58</v>
       </c>
       <c r="AN127">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AO127">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AP127">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AQ127">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR127">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AS127">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AT127">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AU127">
         <v>2</v>
@@ -27451,22 +27451,22 @@
         <v>2.4</v>
       </c>
       <c r="AN128">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AO128">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AP128">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ128">
         <v>1.09</v>
       </c>
       <c r="AR128">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AS128">
-        <v>0.96</v>
+        <v>1.11</v>
       </c>
       <c r="AT128">
         <v>2.38</v>
@@ -27657,25 +27657,25 @@
         <v>1.41</v>
       </c>
       <c r="AN129">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AO129">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AP129">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="AQ129">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AR129">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AS129">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AT129">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27863,25 +27863,25 @@
         <v>1.73</v>
       </c>
       <c r="AN130">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AO130">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AP130">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AQ130">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR130">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS130">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AT130">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28069,25 +28069,25 @@
         <v>4.75</v>
       </c>
       <c r="AN131">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AO131">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AP131">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="AQ131">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR131">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AS131">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AT131">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="AU131">
         <v>7</v>
@@ -28275,25 +28275,25 @@
         <v>1.05</v>
       </c>
       <c r="AN132">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AO132">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AP132">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ132">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AR132">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AS132">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AT132">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="AU132">
         <v>3</v>
@@ -28481,25 +28481,25 @@
         <v>1.02</v>
       </c>
       <c r="AN133">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AO133">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AQ133">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR133">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AS133">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AT133">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="AU133">
         <v>2</v>
@@ -28687,22 +28687,22 @@
         <v>1.52</v>
       </c>
       <c r="AN134">
+        <v>1.23</v>
+      </c>
+      <c r="AO134">
         <v>1.55</v>
       </c>
-      <c r="AO134">
-        <v>1.45</v>
-      </c>
       <c r="AP134">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AQ134">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR134">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AS134">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AT134">
         <v>2.43</v>
@@ -28893,25 +28893,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AO135">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AP135">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AQ135">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AR135">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS135">
         <v>1.15</v>
       </c>
       <c r="AT135">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29099,25 +29099,25 @@
         <v>7.25</v>
       </c>
       <c r="AN136">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="AO136">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="AP136">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="AR136">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AS136">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AT136">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29305,25 +29305,25 @@
         <v>1.6</v>
       </c>
       <c r="AN137">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO137">
-        <v>0.73</v>
+        <v>1.05</v>
       </c>
       <c r="AP137">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="AR137">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AS137">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="AT137">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29511,25 +29511,25 @@
         <v>1.04</v>
       </c>
       <c r="AN138">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AO138">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="AP138">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ138">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="AR138">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AS138">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AT138">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="AU138">
         <v>6</v>
@@ -29717,25 +29717,25 @@
         <v>3.7</v>
       </c>
       <c r="AN139">
-        <v>2.82</v>
+        <v>2</v>
       </c>
       <c r="AO139">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="AP139">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="AQ139">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AR139">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS139">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AT139">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AU139">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Scotland Premiership_20242025.xlsx
@@ -1501,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3">
         <v>1.09</v>
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ4">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ5">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ6">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ7">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2731,25 +2731,25 @@
         <v>4.33</v>
       </c>
       <c r="AN8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ8">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>10</v>
@@ -2937,25 +2937,25 @@
         <v>1.5</v>
       </c>
       <c r="AN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>6</v>
@@ -3143,25 +3143,25 @@
         <v>1.36</v>
       </c>
       <c r="AN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>8</v>
@@ -3352,22 +3352,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>0</v>
@@ -3555,25 +3555,25 @@
         <v>1.95</v>
       </c>
       <c r="AN12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR12">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>4</v>
@@ -3767,19 +3767,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ13">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR13">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>3</v>
@@ -3970,22 +3970,22 @@
         <v>1</v>
       </c>
       <c r="AO14">
+        <v>3</v>
+      </c>
+      <c r="AP14">
+        <v>1.64</v>
+      </c>
+      <c r="AQ14">
+        <v>0.67</v>
+      </c>
+      <c r="AR14">
+        <v>2.04</v>
+      </c>
+      <c r="AS14">
         <v>1.5</v>
       </c>
-      <c r="AP14">
-        <v>1.61</v>
-      </c>
-      <c r="AQ14">
-        <v>0.65</v>
-      </c>
-      <c r="AR14">
-        <v>1.54</v>
-      </c>
-      <c r="AS14">
-        <v>1.44</v>
-      </c>
       <c r="AT14">
-        <v>2.98</v>
+        <v>3.54</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4176,22 +4176,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR15">
-        <v>1</v>
+        <v>0.53</v>
       </c>
       <c r="AS15">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AT15">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="AU15">
         <v>3</v>
@@ -4379,25 +4379,25 @@
         <v>4.5</v>
       </c>
       <c r="AN16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO16">
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
       </c>
       <c r="AR16">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AS16">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AT16">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="AU16">
         <v>10</v>
@@ -4585,25 +4585,25 @@
         <v>1.02</v>
       </c>
       <c r="AN17">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AS17">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AT17">
-        <v>3.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU17">
         <v>2</v>
@@ -4791,25 +4791,25 @@
         <v>1.4</v>
       </c>
       <c r="AN18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ18">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AS18">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AT18">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="AU18">
         <v>7</v>
@@ -5003,19 +5003,19 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ19">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR19">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="AS19">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT19">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -5203,25 +5203,25 @@
         <v>1.73</v>
       </c>
       <c r="AN20">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR20">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AS20">
-        <v>0.91</v>
+        <v>1.22</v>
       </c>
       <c r="AT20">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="AU20">
         <v>6</v>
@@ -5409,25 +5409,25 @@
         <v>1.42</v>
       </c>
       <c r="AN21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ21">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR21">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AS21">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="AT21">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="AU21">
         <v>6</v>
@@ -5615,25 +5615,25 @@
         <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO22">
         <v>3</v>
       </c>
       <c r="AP22">
+        <v>1.08</v>
+      </c>
+      <c r="AQ22">
         <v>1.09</v>
       </c>
-      <c r="AQ22">
-        <v>1.52</v>
-      </c>
       <c r="AR22">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="AS22">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AT22">
-        <v>2.46</v>
+        <v>3.43</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5824,22 +5824,22 @@
         <v>3</v>
       </c>
       <c r="AO23">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ23">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR23">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS23">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="AT23">
-        <v>3.96</v>
+        <v>4.28</v>
       </c>
       <c r="AU23">
         <v>5</v>
@@ -6027,25 +6027,25 @@
         <v>2</v>
       </c>
       <c r="AN24">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AS24">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT24">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="AU24">
         <v>3</v>
@@ -6236,22 +6236,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
+        <v>1.45</v>
+      </c>
+      <c r="AQ25">
         <v>1.09</v>
       </c>
-      <c r="AQ25">
-        <v>1.26</v>
-      </c>
       <c r="AR25">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="AS25">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="AT25">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AU25">
         <v>4</v>
@@ -6442,22 +6442,22 @@
         <v>3</v>
       </c>
       <c r="AO26">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR26">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AS26">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AT26">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6648,22 +6648,22 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ27">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AS27">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AT27">
-        <v>3.19</v>
+        <v>3.36</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6854,22 +6854,22 @@
         <v>0.5</v>
       </c>
       <c r="AO28">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ28">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR28">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AS28">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT28">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7060,22 +7060,22 @@
         <v>0.5</v>
       </c>
       <c r="AO29">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP29">
+        <v>1.08</v>
+      </c>
+      <c r="AQ29">
         <v>1.09</v>
       </c>
-      <c r="AQ29">
-        <v>1.17</v>
-      </c>
       <c r="AR29">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AS29">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AT29">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7263,25 +7263,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ30">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR30">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>0.85</v>
       </c>
       <c r="AT30">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="AU30">
         <v>4</v>
@@ -7472,22 +7472,22 @@
         <v>2</v>
       </c>
       <c r="AO31">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ31">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AS31">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AT31">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="AU31">
         <v>0</v>
@@ -7675,25 +7675,25 @@
         <v>1.75</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO32">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AS32">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AT32">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AU32">
         <v>7</v>
@@ -7881,25 +7881,25 @@
         <v>1.41</v>
       </c>
       <c r="AN33">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO33">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
       <c r="AS33">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AT33">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AU33">
         <v>3</v>
@@ -8087,25 +8087,25 @@
         <v>2.25</v>
       </c>
       <c r="AN34">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
         <v>1.09</v>
       </c>
       <c r="AR34">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AS34">
-        <v>1.21</v>
+        <v>0.84</v>
       </c>
       <c r="AT34">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8293,25 +8293,25 @@
         <v>1.66</v>
       </c>
       <c r="AN35">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO35">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP35">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ35">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR35">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AS35">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AT35">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AU35">
         <v>4</v>
@@ -8499,25 +8499,25 @@
         <v>1.58</v>
       </c>
       <c r="AN36">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO36">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP36">
+        <v>1.64</v>
+      </c>
+      <c r="AQ36">
+        <v>0.91</v>
+      </c>
+      <c r="AR36">
+        <v>1.45</v>
+      </c>
+      <c r="AS36">
         <v>1.35</v>
       </c>
-      <c r="AQ36">
-        <v>1.17</v>
-      </c>
-      <c r="AR36">
-        <v>1.34</v>
-      </c>
-      <c r="AS36">
-        <v>1.08</v>
-      </c>
       <c r="AT36">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AU36">
         <v>5</v>
@@ -8705,25 +8705,25 @@
         <v>1.45</v>
       </c>
       <c r="AN37">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AO37">
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR37">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AS37">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT37">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8911,25 +8911,25 @@
         <v>1.04</v>
       </c>
       <c r="AN38">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO38">
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ38">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR38">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AS38">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AT38">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="AU38">
         <v>2</v>
@@ -9117,25 +9117,25 @@
         <v>2.9</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ39">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR39">
-        <v>1.59</v>
+        <v>2.01</v>
       </c>
       <c r="AS39">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AT39">
-        <v>2.79</v>
+        <v>3.33</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9323,25 +9323,25 @@
         <v>1.63</v>
       </c>
       <c r="AN40">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ40">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
-        <v>1.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS40">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AT40">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AU40">
         <v>4</v>
@@ -9529,25 +9529,25 @@
         <v>1.77</v>
       </c>
       <c r="AN41">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO41">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP41">
+        <v>1.42</v>
+      </c>
+      <c r="AQ41">
+        <v>1.08</v>
+      </c>
+      <c r="AR41">
+        <v>1.12</v>
+      </c>
+      <c r="AS41">
         <v>1.26</v>
       </c>
-      <c r="AQ41">
-        <v>1.35</v>
-      </c>
-      <c r="AR41">
-        <v>1.24</v>
-      </c>
-      <c r="AS41">
-        <v>1.28</v>
-      </c>
       <c r="AT41">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9735,25 +9735,25 @@
         <v>1.62</v>
       </c>
       <c r="AN42">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO42">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR42">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AS42">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="AT42">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AU42">
         <v>4</v>
@@ -9941,25 +9941,25 @@
         <v>1.02</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO43">
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ43">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR43">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AS43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AT43">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="AU43">
         <v>6</v>
@@ -10150,22 +10150,22 @@
         <v>3</v>
       </c>
       <c r="AO44">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ44">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AS44">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AT44">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="AU44">
         <v>4</v>
@@ -10353,25 +10353,25 @@
         <v>5.7</v>
       </c>
       <c r="AN45">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="AO45">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ45">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR45">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AS45">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AT45">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AU45">
         <v>7</v>
@@ -10565,19 +10565,19 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ46">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AS46">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AT46">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10765,25 +10765,25 @@
         <v>1.57</v>
       </c>
       <c r="AN47">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AO47">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR47">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AS47">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT47">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10971,25 +10971,25 @@
         <v>2</v>
       </c>
       <c r="AN48">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
       <c r="AO48">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ48">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR48">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AS48">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AT48">
-        <v>2.57</v>
+        <v>3.21</v>
       </c>
       <c r="AU48">
         <v>5</v>
@@ -11177,25 +11177,25 @@
         <v>1.83</v>
       </c>
       <c r="AN49">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO49">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ49">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR49">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS49">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT49">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="AU49">
         <v>4</v>
@@ -11383,25 +11383,25 @@
         <v>1.5</v>
       </c>
       <c r="AN50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO50">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="AP50">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
       </c>
       <c r="AR50">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AS50">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="AT50">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AU50">
         <v>8</v>
@@ -11589,25 +11589,25 @@
         <v>1.12</v>
       </c>
       <c r="AN51">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="AO51">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ51">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR51">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AS51">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AT51">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11795,25 +11795,25 @@
         <v>2.15</v>
       </c>
       <c r="AN52">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP52">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR52">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS52">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AT52">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12001,25 +12001,25 @@
         <v>1.36</v>
       </c>
       <c r="AN53">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AO53">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ53">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR53">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AS53">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT53">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AU53">
         <v>4</v>
@@ -12207,25 +12207,25 @@
         <v>2.2</v>
       </c>
       <c r="AN54">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AO54">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ54">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR54">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS54">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT54">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AU54">
         <v>6</v>
@@ -12413,25 +12413,25 @@
         <v>1.6</v>
       </c>
       <c r="AN55">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="AO55">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ55">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR55">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AS55">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AT55">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12619,25 +12619,25 @@
         <v>1.02</v>
       </c>
       <c r="AN56">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO56">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ56">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
       </c>
       <c r="AS56">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AT56">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="AU56">
         <v>3</v>
@@ -12825,25 +12825,25 @@
         <v>4</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO57">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ57">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR57">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AS57">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AT57">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13031,25 +13031,25 @@
         <v>1.93</v>
       </c>
       <c r="AN58">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP58">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR58">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AS58">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT58">
-        <v>2.48</v>
+        <v>2.71</v>
       </c>
       <c r="AU58">
         <v>6</v>
@@ -13237,25 +13237,25 @@
         <v>1.33</v>
       </c>
       <c r="AN59">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO59">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AP59">
+        <v>1.08</v>
+      </c>
+      <c r="AQ59">
         <v>1.09</v>
       </c>
-      <c r="AQ59">
-        <v>1.26</v>
-      </c>
       <c r="AR59">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AS59">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AT59">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="AU59">
         <v>3</v>
@@ -13443,25 +13443,25 @@
         <v>2.05</v>
       </c>
       <c r="AN60">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ60">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR60">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AS60">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AT60">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AU60">
         <v>6</v>
@@ -13649,25 +13649,25 @@
         <v>1.67</v>
       </c>
       <c r="AN61">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO61">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ61">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AS61">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AT61">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13855,25 +13855,25 @@
         <v>6.25</v>
       </c>
       <c r="AN62">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP62">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR62">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AS62">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AT62">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14061,25 +14061,25 @@
         <v>1.25</v>
       </c>
       <c r="AN63">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AO63">
-        <v>2.11</v>
+        <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ63">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR63">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AS63">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AT63">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="AU63">
         <v>7</v>
@@ -14267,25 +14267,25 @@
         <v>1.22</v>
       </c>
       <c r="AN64">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="AO64">
-        <v>0.55</v>
+        <v>0.17</v>
       </c>
       <c r="AP64">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ64">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AS64">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AT64">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14473,25 +14473,25 @@
         <v>2.05</v>
       </c>
       <c r="AN65">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO65">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
       </c>
       <c r="AR65">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AS65">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
       <c r="AT65">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14679,25 +14679,25 @@
         <v>1.53</v>
       </c>
       <c r="AN66">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AO66">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP66">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR66">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AS66">
         <v>1.21</v>
       </c>
       <c r="AT66">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14885,25 +14885,25 @@
         <v>2</v>
       </c>
       <c r="AN67">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AO67">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ67">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR67">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AS67">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AT67">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AU67">
         <v>4</v>
@@ -15091,25 +15091,25 @@
         <v>2.05</v>
       </c>
       <c r="AN68">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP68">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ68">
         <v>1.09</v>
       </c>
       <c r="AR68">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AS68">
-        <v>1.1</v>
+        <v>0.82</v>
       </c>
       <c r="AT68">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15297,25 +15297,25 @@
         <v>1.93</v>
       </c>
       <c r="AN69">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ69">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR69">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS69">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AT69">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AU69">
         <v>3</v>
@@ -15503,25 +15503,25 @@
         <v>1.95</v>
       </c>
       <c r="AN70">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO70">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ70">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR70">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AS70">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AT70">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AU70">
         <v>5</v>
@@ -15709,25 +15709,25 @@
         <v>2.15</v>
       </c>
       <c r="AN71">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AO71">
+        <v>1</v>
+      </c>
+      <c r="AP71">
+        <v>1.92</v>
+      </c>
+      <c r="AQ71">
         <v>1.09</v>
       </c>
-      <c r="AP71">
-        <v>1.52</v>
-      </c>
-      <c r="AQ71">
-        <v>1.17</v>
-      </c>
       <c r="AR71">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS71">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AT71">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15915,25 +15915,25 @@
         <v>1.07</v>
       </c>
       <c r="AN72">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AO72">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AP72">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ72">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR72">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS72">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AT72">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -16121,25 +16121,25 @@
         <v>2.88</v>
       </c>
       <c r="AN73">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AO73">
+        <v>0.57</v>
+      </c>
+      <c r="AP73">
+        <v>2.83</v>
+      </c>
+      <c r="AQ73">
         <v>0.75</v>
       </c>
-      <c r="AP73">
-        <v>2.04</v>
-      </c>
-      <c r="AQ73">
-        <v>1.04</v>
-      </c>
       <c r="AR73">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AS73">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AT73">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AU73">
         <v>4</v>
@@ -16327,25 +16327,25 @@
         <v>1.36</v>
       </c>
       <c r="AN74">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="AO74">
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ74">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR74">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AS74">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AT74">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16533,25 +16533,25 @@
         <v>1.45</v>
       </c>
       <c r="AN75">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AO75">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AP75">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ75">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR75">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AS75">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AT75">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="AU75">
         <v>-1</v>
@@ -16739,25 +16739,25 @@
         <v>3.75</v>
       </c>
       <c r="AN76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO76">
+        <v>1.5</v>
+      </c>
+      <c r="AP76">
+        <v>2.83</v>
+      </c>
+      <c r="AQ76">
         <v>1.58</v>
       </c>
-      <c r="AP76">
-        <v>2.04</v>
-      </c>
-      <c r="AQ76">
-        <v>1.61</v>
-      </c>
       <c r="AR76">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AS76">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AT76">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="AU76">
         <v>12</v>
@@ -16945,25 +16945,25 @@
         <v>1.38</v>
       </c>
       <c r="AN77">
+        <v>1.57</v>
+      </c>
+      <c r="AO77">
+        <v>2.5</v>
+      </c>
+      <c r="AP77">
+        <v>1.42</v>
+      </c>
+      <c r="AQ77">
+        <v>1.09</v>
+      </c>
+      <c r="AR77">
+        <v>1.13</v>
+      </c>
+      <c r="AS77">
         <v>1.15</v>
       </c>
-      <c r="AO77">
-        <v>2.82</v>
-      </c>
-      <c r="AP77">
-        <v>1.17</v>
-      </c>
-      <c r="AQ77">
-        <v>1.52</v>
-      </c>
-      <c r="AR77">
-        <v>1.19</v>
-      </c>
-      <c r="AS77">
-        <v>1.32</v>
-      </c>
       <c r="AT77">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="AU77">
         <v>6</v>
@@ -17151,25 +17151,25 @@
         <v>1.47</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO78">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="AP78">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ78">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR78">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AS78">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AT78">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AU78">
         <v>-1</v>
@@ -17357,25 +17357,25 @@
         <v>1.09</v>
       </c>
       <c r="AN79">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ79">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR79">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AS79">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AT79">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AU79">
         <v>-1</v>
@@ -17563,25 +17563,25 @@
         <v>1.55</v>
       </c>
       <c r="AN80">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="AO80">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AP80">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ80">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR80">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS80">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT80">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17769,25 +17769,25 @@
         <v>7.5</v>
       </c>
       <c r="AN81">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AO81">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ81">
         <v>1.09</v>
       </c>
       <c r="AR81">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AS81">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT81">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="AU81">
         <v>10</v>
@@ -17975,25 +17975,25 @@
         <v>1.68</v>
       </c>
       <c r="AN82">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AO82">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ82">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR82">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AS82">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AT82">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AU82">
         <v>7</v>
@@ -18181,25 +18181,25 @@
         <v>1.8</v>
       </c>
       <c r="AN83">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AO83">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="AP83">
+        <v>1.45</v>
+      </c>
+      <c r="AQ83">
         <v>1.09</v>
       </c>
-      <c r="AQ83">
-        <v>1.17</v>
-      </c>
       <c r="AR83">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AS83">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AT83">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18387,25 +18387,25 @@
         <v>1.53</v>
       </c>
       <c r="AN84">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AO84">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ84">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR84">
         <v>1.24</v>
       </c>
       <c r="AS84">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AT84">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AU84">
         <v>4</v>
@@ -18593,25 +18593,25 @@
         <v>1.03</v>
       </c>
       <c r="AN85">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.92</v>
+        <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ85">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR85">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AS85">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AT85">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AU85">
         <v>2</v>
@@ -18799,25 +18799,25 @@
         <v>1.6</v>
       </c>
       <c r="AN86">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AO86">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AP86">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ86">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR86">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AS86">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AT86">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="AU86">
         <v>4</v>
@@ -19005,25 +19005,25 @@
         <v>3.75</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AO87">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AP87">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ87">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR87">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="AS87">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AT87">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="AU87">
         <v>12</v>
@@ -19211,25 +19211,25 @@
         <v>1.75</v>
       </c>
       <c r="AN88">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AO88">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR88">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AS88">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AT88">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19417,25 +19417,25 @@
         <v>1.11</v>
       </c>
       <c r="AN89">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="AO89">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ89">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR89">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AS89">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AT89">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AU89">
         <v>5</v>
@@ -19623,25 +19623,25 @@
         <v>1.68</v>
       </c>
       <c r="AN90">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AO90">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ90">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.21</v>
       </c>
       <c r="AS90">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AT90">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AU90">
         <v>7</v>
@@ -19829,25 +19829,25 @@
         <v>2.4</v>
       </c>
       <c r="AN91">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AO91">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AP91">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ91">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AS91">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AT91">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -20035,25 +20035,25 @@
         <v>5.75</v>
       </c>
       <c r="AN92">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AO92">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="AP92">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ92">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR92">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AS92">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AT92">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="AU92">
         <v>12</v>
@@ -20241,25 +20241,25 @@
         <v>1.66</v>
       </c>
       <c r="AN93">
+        <v>1.86</v>
+      </c>
+      <c r="AO93">
+        <v>0.78</v>
+      </c>
+      <c r="AP93">
         <v>1.64</v>
       </c>
-      <c r="AO93">
-        <v>0.87</v>
-      </c>
-      <c r="AP93">
-        <v>1.61</v>
-      </c>
       <c r="AQ93">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR93">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AS93">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AT93">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AU93">
         <v>8</v>
@@ -20447,25 +20447,25 @@
         <v>1.87</v>
       </c>
       <c r="AN94">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AO94">
-        <v>1.27</v>
+        <v>0.86</v>
       </c>
       <c r="AP94">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR94">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AS94">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT94">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="AU94">
         <v>9</v>
@@ -20653,25 +20653,25 @@
         <v>1.03</v>
       </c>
       <c r="AN95">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO95">
-        <v>2.07</v>
+        <v>1.17</v>
       </c>
       <c r="AP95">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ95">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR95">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AS95">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AT95">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AU95">
         <v>3</v>
@@ -20859,25 +20859,25 @@
         <v>1.45</v>
       </c>
       <c r="AN96">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="AO96">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ96">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR96">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AS96">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT96">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -21065,25 +21065,25 @@
         <v>2.45</v>
       </c>
       <c r="AN97">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AO97">
-        <v>0.9399999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="AP97">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ97">
         <v>1.09</v>
       </c>
       <c r="AR97">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AS97">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="AT97">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="AU97">
         <v>8</v>
@@ -21271,25 +21271,25 @@
         <v>1.52</v>
       </c>
       <c r="AN98">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AO98">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AP98">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ98">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR98">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AS98">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AT98">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AU98">
         <v>7</v>
@@ -21477,25 +21477,25 @@
         <v>1.35</v>
       </c>
       <c r="AN99">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO99">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ99">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR99">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS99">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="AT99">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21683,25 +21683,25 @@
         <v>1.57</v>
       </c>
       <c r="AN100">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AO100">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ100">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR100">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AS100">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AT100">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="AU100">
         <v>2</v>
@@ -21889,25 +21889,25 @@
         <v>1.36</v>
       </c>
       <c r="AN101">
+        <v>1.33</v>
+      </c>
+      <c r="AO101">
         <v>0.88</v>
       </c>
-      <c r="AO101">
+      <c r="AP101">
+        <v>1.08</v>
+      </c>
+      <c r="AQ101">
+        <v>0.91</v>
+      </c>
+      <c r="AR101">
         <v>1.24</v>
       </c>
-      <c r="AP101">
-        <v>1.09</v>
-      </c>
-      <c r="AQ101">
-        <v>1.17</v>
-      </c>
-      <c r="AR101">
-        <v>1.03</v>
-      </c>
       <c r="AS101">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT101">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22095,25 +22095,25 @@
         <v>4.5</v>
       </c>
       <c r="AN102">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="AO102">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ102">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR102">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AS102">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AT102">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22301,25 +22301,25 @@
         <v>1.65</v>
       </c>
       <c r="AN103">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="AO103">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="AP103">
+        <v>1.92</v>
+      </c>
+      <c r="AQ103">
+        <v>1.09</v>
+      </c>
+      <c r="AR103">
+        <v>1.34</v>
+      </c>
+      <c r="AS103">
         <v>1.52</v>
       </c>
-      <c r="AQ103">
-        <v>1.26</v>
-      </c>
-      <c r="AR103">
-        <v>1.32</v>
-      </c>
-      <c r="AS103">
-        <v>1.49</v>
-      </c>
       <c r="AT103">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AU103">
         <v>3</v>
@@ -22507,25 +22507,25 @@
         <v>1.01</v>
       </c>
       <c r="AN104">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO104">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AP104">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR104">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AS104">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AT104">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="AU104">
         <v>3</v>
@@ -22713,25 +22713,25 @@
         <v>2.55</v>
       </c>
       <c r="AN105">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="AO105">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="AP105">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR105">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AS105">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AT105">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="AU105">
         <v>7</v>
@@ -22919,25 +22919,25 @@
         <v>1.74</v>
       </c>
       <c r="AN106">
+        <v>1.33</v>
+      </c>
+      <c r="AO106">
         <v>0.89</v>
       </c>
-      <c r="AO106">
-        <v>1</v>
-      </c>
       <c r="AP106">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ106">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR106">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AS106">
         <v>1.47</v>
       </c>
       <c r="AT106">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23125,25 +23125,25 @@
         <v>6.1</v>
       </c>
       <c r="AN107">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AO107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP107">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ107">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR107">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AS107">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AT107">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="AU107">
         <v>8</v>
@@ -23331,25 +23331,25 @@
         <v>2</v>
       </c>
       <c r="AN108">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="AO108">
-        <v>0.83</v>
+        <v>0.38</v>
       </c>
       <c r="AP108">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>1.09</v>
       </c>
       <c r="AR108">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AS108">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT108">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AU108">
         <v>3</v>
@@ -23537,25 +23537,25 @@
         <v>1.48</v>
       </c>
       <c r="AN109">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO109">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AP109">
+        <v>1.45</v>
+      </c>
+      <c r="AQ109">
         <v>1.09</v>
       </c>
-      <c r="AQ109">
-        <v>1.52</v>
-      </c>
       <c r="AR109">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AS109">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT109">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU109">
         <v>9</v>
@@ -23743,25 +23743,25 @@
         <v>1.4</v>
       </c>
       <c r="AN110">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AO110">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AP110">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ110">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR110">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AS110">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AT110">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AU110">
         <v>5</v>
@@ -23949,25 +23949,25 @@
         <v>1.08</v>
       </c>
       <c r="AN111">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AO111">
-        <v>2.19</v>
+        <v>1.43</v>
       </c>
       <c r="AP111">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ111">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR111">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AS111">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AT111">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="AU111">
         <v>4</v>
@@ -24155,25 +24155,25 @@
         <v>1.22</v>
       </c>
       <c r="AN112">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="AO112">
-        <v>0.84</v>
+        <v>0.44</v>
       </c>
       <c r="AP112">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR112">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AS112">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AT112">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AU112">
         <v>5</v>
@@ -24361,25 +24361,25 @@
         <v>6.75</v>
       </c>
       <c r="AN113">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AO113">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ113">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AS113">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AT113">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU113">
         <v>12</v>
@@ -24570,22 +24570,22 @@
         <v>1.11</v>
       </c>
       <c r="AO114">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="AP114">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ114">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR114">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS114">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AT114">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU114">
         <v>3</v>
@@ -24773,25 +24773,25 @@
         <v>1.07</v>
       </c>
       <c r="AN115">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO115">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="AP115">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ115">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AS115">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AT115">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -24979,25 +24979,25 @@
         <v>1.68</v>
       </c>
       <c r="AN116">
+        <v>1.7</v>
+      </c>
+      <c r="AO116">
+        <v>0.67</v>
+      </c>
+      <c r="AP116">
         <v>1.42</v>
       </c>
-      <c r="AO116">
-        <v>1.06</v>
-      </c>
-      <c r="AP116">
-        <v>1.17</v>
-      </c>
       <c r="AQ116">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AR116">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AS116">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT116">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AU116">
         <v>6</v>
@@ -25185,22 +25185,22 @@
         <v>1.44</v>
       </c>
       <c r="AN117">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AO117">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ117">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR117">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AS117">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AT117">
         <v>2.58</v>
@@ -25391,25 +25391,25 @@
         <v>1.73</v>
       </c>
       <c r="AN118">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO118">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AP118">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ118">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR118">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AS118">
         <v>1.22</v>
       </c>
       <c r="AT118">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AU118">
         <v>6</v>
@@ -25597,25 +25597,25 @@
         <v>1.27</v>
       </c>
       <c r="AN119">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AO119">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AQ119">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AR119">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS119">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT119">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU119">
         <v>3</v>
@@ -25803,25 +25803,25 @@
         <v>1.98</v>
       </c>
       <c r="AN120">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="AO120">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AQ120">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR120">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AS120">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AT120">
-        <v>2.57</v>
+        <v>2.87</v>
       </c>
       <c r="AU120">
         <v>7</v>
@@ -26009,25 +26009,25 @@
         <v>1.47</v>
       </c>
       <c r="AN121">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="AO121">
         <v>2.78</v>
       </c>
       <c r="AP121">
+        <v>2.83</v>
+      </c>
+      <c r="AQ121">
+        <v>2.42</v>
+      </c>
+      <c r="AR121">
         <v>2.04</v>
       </c>
-      <c r="AQ121">
-        <v>2.61</v>
-      </c>
-      <c r="AR121">
-        <v>1.89</v>
-      </c>
       <c r="AS121">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AT121">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="AU121">
         <v>10</v>
@@ -26215,25 +26215,25 @@
         <v>2.5</v>
       </c>
       <c r="AN122">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AO122">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ122">
         <v>1.09</v>
       </c>
       <c r="AR122">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AS122">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="AT122">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AU122">
         <v>5</v>
@@ -26421,25 +26421,25 @@
         <v>1.5</v>
       </c>
       <c r="AN123">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AO123">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AP123">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ123">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR123">
+        <v>1.36</v>
+      </c>
+      <c r="AS123">
         <v>1.22</v>
       </c>
-      <c r="AS123">
-        <v>1.29</v>
-      </c>
       <c r="AT123">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="AU123">
         <v>5</v>
@@ -26627,25 +26627,25 @@
         <v>1.11</v>
       </c>
       <c r="AN124">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AO124">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="AP124">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ124">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR124">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AS124">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AT124">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -26833,25 +26833,25 @@
         <v>1.47</v>
       </c>
       <c r="AN125">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AO125">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AP125">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AQ125">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR125">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AS125">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT125">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AU125">
         <v>4</v>
@@ -27039,25 +27039,25 @@
         <v>5.25</v>
       </c>
       <c r="AN126">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AO126">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP126">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ126">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="AR126">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="AS126">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AT126">
-        <v>3.26</v>
+        <v>3.52</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27245,25 +27245,25 @@
         <v>1.58</v>
       </c>
       <c r="AN127">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AO127">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR127">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AS127">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AT127">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AU127">
         <v>2</v>
@@ -27451,22 +27451,22 @@
         <v>2.4</v>
       </c>
       <c r="AN128">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="AO128">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AP128">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ128">
         <v>1.09</v>
       </c>
       <c r="AR128">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AS128">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="AT128">
         <v>2.38</v>
@@ -27657,25 +27657,25 @@
         <v>1.41</v>
       </c>
       <c r="AN129">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="AO129">
+        <v>0.9</v>
+      </c>
+      <c r="AP129">
+        <v>0.64</v>
+      </c>
+      <c r="AQ129">
+        <v>1.09</v>
+      </c>
+      <c r="AR129">
+        <v>1.19</v>
+      </c>
+      <c r="AS129">
         <v>1.1</v>
       </c>
-      <c r="AP129">
-        <v>0.65</v>
-      </c>
-      <c r="AQ129">
-        <v>1.17</v>
-      </c>
-      <c r="AR129">
-        <v>1.11</v>
-      </c>
-      <c r="AS129">
-        <v>1.23</v>
-      </c>
       <c r="AT129">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AU129">
         <v>6</v>
@@ -27863,25 +27863,25 @@
         <v>1.73</v>
       </c>
       <c r="AN130">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AO130">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AP130">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AQ130">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR130">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AS130">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AT130">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AU130">
         <v>4</v>
@@ -28069,25 +28069,25 @@
         <v>4.75</v>
       </c>
       <c r="AN131">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AO131">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="AQ131">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR131">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AS131">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AT131">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="AU131">
         <v>7</v>
@@ -28275,25 +28275,25 @@
         <v>1.05</v>
       </c>
       <c r="AN132">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AO132">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AP132">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ132">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="AR132">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AS132">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AT132">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AU132">
         <v>3</v>
@@ -28481,25 +28481,25 @@
         <v>1.02</v>
       </c>
       <c r="AN133">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AO133">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AP133">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR133">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AS133">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AT133">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="AU133">
         <v>2</v>
@@ -28687,22 +28687,22 @@
         <v>1.52</v>
       </c>
       <c r="AN134">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AO134">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AP134">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ134">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR134">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AS134">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AT134">
         <v>2.43</v>
@@ -28893,25 +28893,25 @@
         <v>1.95</v>
       </c>
       <c r="AN135">
+        <v>1.27</v>
+      </c>
+      <c r="AO135">
         <v>1.18</v>
       </c>
-      <c r="AO135">
-        <v>1.41</v>
-      </c>
       <c r="AP135">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AQ135">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR135">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AS135">
         <v>1.15</v>
       </c>
       <c r="AT135">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29099,25 +29099,25 @@
         <v>7.25</v>
       </c>
       <c r="AN136">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AO136">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="AP136">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ136">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AS136">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AT136">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29305,25 +29305,25 @@
         <v>1.6</v>
       </c>
       <c r="AN137">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO137">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="AP137">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AQ137">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="AR137">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AS137">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="AT137">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29511,25 +29511,25 @@
         <v>1.04</v>
       </c>
       <c r="AN138">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AO138">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AP138">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ138">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AR138">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AS138">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT138">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="AU138">
         <v>6</v>
@@ -29717,25 +29717,25 @@
         <v>3.7</v>
       </c>
       <c r="AN139">
-        <v>2</v>
+        <v>2.82</v>
       </c>
       <c r="AO139">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="AQ139">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AR139">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AS139">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AT139">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AU139">
         <v>13</v>
